--- a/gstdatabase/GSTR-1-2025-2026.xlsx
+++ b/gstdatabase/GSTR-1-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B7F230-AF9F-4EC7-A00B-A9B72350E7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A38B39F-4423-459F-BE7F-B87C09944EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -360,6 +360,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -371,15 +380,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -759,10 +759,10 @@
       <c r="AZ2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -967,100 +967,100 @@
       <c r="AZ6" s="1"/>
     </row>
     <row r="8" spans="1:62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="17">
         <v>45748</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="14">
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="17">
         <v>45778</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="14">
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="17">
         <v>45809</v>
       </c>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="14">
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="17">
         <v>45839</v>
       </c>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="14">
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="17">
         <v>45870</v>
       </c>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="14">
+      <c r="X8" s="18"/>
+      <c r="Y8" s="18"/>
+      <c r="Z8" s="18"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="17">
         <v>45901</v>
       </c>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="14">
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="18"/>
+      <c r="AE8" s="18"/>
+      <c r="AF8" s="19"/>
+      <c r="AG8" s="17">
         <v>45931</v>
       </c>
-      <c r="AH8" s="15"/>
-      <c r="AI8" s="15"/>
-      <c r="AJ8" s="15"/>
-      <c r="AK8" s="16"/>
-      <c r="AL8" s="14">
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="18"/>
+      <c r="AK8" s="19"/>
+      <c r="AL8" s="17">
         <v>45962</v>
       </c>
-      <c r="AM8" s="15"/>
-      <c r="AN8" s="15"/>
-      <c r="AO8" s="15"/>
-      <c r="AP8" s="16"/>
-      <c r="AQ8" s="14">
+      <c r="AM8" s="18"/>
+      <c r="AN8" s="18"/>
+      <c r="AO8" s="18"/>
+      <c r="AP8" s="19"/>
+      <c r="AQ8" s="17">
         <v>45992</v>
       </c>
-      <c r="AR8" s="15"/>
-      <c r="AS8" s="15"/>
-      <c r="AT8" s="15"/>
-      <c r="AU8" s="16"/>
-      <c r="AV8" s="14">
+      <c r="AR8" s="18"/>
+      <c r="AS8" s="18"/>
+      <c r="AT8" s="18"/>
+      <c r="AU8" s="19"/>
+      <c r="AV8" s="17">
         <v>46023</v>
       </c>
-      <c r="AW8" s="15"/>
-      <c r="AX8" s="15"/>
-      <c r="AY8" s="15"/>
-      <c r="AZ8" s="16"/>
-      <c r="BA8" s="14">
+      <c r="AW8" s="18"/>
+      <c r="AX8" s="18"/>
+      <c r="AY8" s="18"/>
+      <c r="AZ8" s="19"/>
+      <c r="BA8" s="17">
         <v>46054</v>
       </c>
-      <c r="BB8" s="15"/>
-      <c r="BC8" s="15"/>
-      <c r="BD8" s="15"/>
-      <c r="BE8" s="16"/>
-      <c r="BF8" s="14">
+      <c r="BB8" s="18"/>
+      <c r="BC8" s="18"/>
+      <c r="BD8" s="18"/>
+      <c r="BE8" s="19"/>
+      <c r="BF8" s="17">
         <v>46082</v>
       </c>
-      <c r="BG8" s="15"/>
-      <c r="BH8" s="15"/>
-      <c r="BI8" s="15"/>
-      <c r="BJ8" s="16"/>
+      <c r="BG8" s="18"/>
+      <c r="BH8" s="18"/>
+      <c r="BI8" s="18"/>
+      <c r="BJ8" s="19"/>
     </row>
     <row r="9" spans="1:62" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>47255</v>
+        <v>47276</v>
       </c>
       <c r="F10" s="5">
-        <v>74145</v>
+        <v>74166</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>0.99940692016336652</v>
+        <v>0.99968998099448703</v>
       </c>
       <c r="H10" s="5">
         <v>75899</v>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>45414</v>
+        <v>45443</v>
       </c>
       <c r="K10" s="5">
-        <v>74881</v>
+        <v>74910</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.98658743856967812</v>
+        <v>0.98696952529018833</v>
       </c>
       <c r="M10" s="5">
         <v>134494</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>88208</v>
+        <v>88260</v>
       </c>
       <c r="P10" s="5">
-        <v>134427</v>
+        <v>134479</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.99950183651315305</v>
+        <v>0.99988847086115362</v>
       </c>
       <c r="R10" s="5">
         <v>73914</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42320</v>
+        <v>42359</v>
       </c>
       <c r="U10" s="5">
-        <v>73647</v>
+        <v>73686</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>0.99638769380631542</v>
+        <v>0.99691533403685362</v>
       </c>
       <c r="W10" s="5">
         <v>75592</v>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>42546</v>
+        <v>42590</v>
       </c>
       <c r="Z10" s="5">
-        <v>74671</v>
+        <v>74715</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.9878161710233887</v>
+        <v>0.98839824320033864</v>
       </c>
       <c r="AB10" s="5">
         <v>136558</v>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>89183</v>
+        <v>89275</v>
       </c>
       <c r="AE10" s="5">
-        <v>136305</v>
+        <v>136397</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99814730737122692</v>
+        <v>0.99882101378168986</v>
       </c>
       <c r="AG10" s="5">
         <v>73704</v>
@@ -1359,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>42437</v>
+        <v>42503</v>
       </c>
       <c r="AJ10" s="5">
-        <v>73424</v>
+        <v>73490</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99620102029740587</v>
+        <v>0.99709649408444589</v>
       </c>
       <c r="AL10" s="5">
         <v>75897</v>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>42902</v>
+        <v>42985</v>
       </c>
       <c r="AO10" s="5">
-        <v>76068</v>
+        <v>76151</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>1.0022530534803746</v>
+        <v>1.003346640842194</v>
       </c>
       <c r="AQ10" s="5">
         <v>140117</v>
@@ -1393,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>91618</v>
+        <v>91820</v>
       </c>
       <c r="AT10" s="5">
-        <v>140641</v>
+        <v>140843</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.0037397317955707</v>
+        <v>1.0051813841289778</v>
       </c>
       <c r="AV10" s="5">
         <v>75508</v>
@@ -1410,14 +1410,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>13568</v>
+        <v>13730</v>
       </c>
       <c r="AY10" s="5">
-        <v>75964</v>
+        <v>76126</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>1.0060390951952112</v>
+        <v>1.0081845632250888</v>
       </c>
       <c r="BA10" s="5">
         <v>78056</v>
@@ -1427,14 +1427,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>43131</v>
+        <v>43368</v>
       </c>
       <c r="BD10" s="5">
-        <v>77570</v>
+        <v>77807</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.99377370093266371</v>
+        <v>0.99680998257661169</v>
       </c>
       <c r="BF10" s="5">
         <v>144885</v>
@@ -1444,14 +1444,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>93699</v>
+        <v>94500</v>
       </c>
       <c r="BI10" s="5">
-        <v>143199</v>
+        <v>144000</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>0.98836318459467853</v>
+        <v>0.9938917072160679</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1469,14 +1469,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>16321</v>
+        <v>16327</v>
       </c>
       <c r="F11" s="5">
-        <v>47485</v>
+        <v>47491</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99268318177067005</v>
+        <v>0.99280861294031564</v>
       </c>
       <c r="H11" s="5">
         <v>49123</v>
@@ -1486,14 +1486,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>16795</v>
+        <v>16802</v>
       </c>
       <c r="K11" s="5">
-        <v>48220</v>
+        <v>48227</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98161757221668056</v>
+        <v>0.9817600716568613</v>
       </c>
       <c r="M11" s="5">
         <v>111861</v>
@@ -1503,14 +1503,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>48251</v>
+        <v>48284</v>
       </c>
       <c r="P11" s="5">
-        <v>111509</v>
+        <v>111542</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99685323750011179</v>
+        <v>0.99714824648447631</v>
       </c>
       <c r="R11" s="5">
         <v>47958</v>
@@ -1520,14 +1520,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15923</v>
+        <v>15936</v>
       </c>
       <c r="U11" s="5">
-        <v>47558</v>
+        <v>47571</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99165936861420412</v>
+        <v>0.9919304391342425</v>
       </c>
       <c r="W11" s="5">
         <v>49731</v>
@@ -1537,14 +1537,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>15229</v>
+        <v>15245</v>
       </c>
       <c r="Z11" s="5">
-        <v>48243</v>
+        <v>48259</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97007902515533573</v>
+        <v>0.97040075606764398</v>
       </c>
       <c r="AB11" s="5">
         <v>113134</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>50485</v>
+        <v>50540</v>
       </c>
       <c r="AE11" s="5">
-        <v>112249</v>
+        <v>112304</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99217741792918135</v>
+        <v>0.99266356709742432</v>
       </c>
       <c r="AG11" s="5">
         <v>48119</v>
@@ -1571,14 +1571,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15441</v>
+        <v>15466</v>
       </c>
       <c r="AJ11" s="5">
-        <v>47649</v>
+        <v>47674</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99023254847357589</v>
+        <v>0.9907520937675347</v>
       </c>
       <c r="AL11" s="5">
         <v>49938</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14847</v>
+        <v>14894</v>
       </c>
       <c r="AO11" s="5">
-        <v>49028</v>
+        <v>49075</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98177740398093638</v>
+        <v>0.98271857102807481</v>
       </c>
       <c r="AQ11" s="5">
         <v>114343</v>
@@ -1605,14 +1605,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>47387</v>
+        <v>47516</v>
       </c>
       <c r="AT11" s="5">
-        <v>114081</v>
+        <v>114210</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99770864853991936</v>
+        <v>0.99883683303743998</v>
       </c>
       <c r="AV11" s="5">
         <v>49251</v>
@@ -1622,14 +1622,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>6893</v>
+        <v>6977</v>
       </c>
       <c r="AY11" s="5">
-        <v>48656</v>
+        <v>48740</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.98791902702483203</v>
+        <v>0.98962457615073807</v>
       </c>
       <c r="BA11" s="5">
         <v>50523</v>
@@ -1639,14 +1639,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>14579</v>
+        <v>14698</v>
       </c>
       <c r="BD11" s="5">
-        <v>49546</v>
+        <v>49665</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.98066227262830785</v>
+        <v>0.98301763553233179</v>
       </c>
       <c r="BF11" s="5">
         <v>116408</v>
@@ -1656,14 +1656,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>48287</v>
+        <v>48850</v>
       </c>
       <c r="BI11" s="5">
-        <v>114716</v>
+        <v>115279</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.9854649165005841</v>
+        <v>0.99030135385884133</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1681,14 +1681,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>44087</v>
+        <v>44106</v>
       </c>
       <c r="F12" s="5">
-        <v>181640</v>
+        <v>181659</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.99393700615054614</v>
+        <v>0.99404097445662876</v>
       </c>
       <c r="H12" s="5">
         <v>186824</v>
@@ -1698,14 +1698,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>41252</v>
+        <v>41276</v>
       </c>
       <c r="K12" s="5">
-        <v>184402</v>
+        <v>184426</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98703592686164521</v>
+        <v>0.98716439001413092</v>
       </c>
       <c r="M12" s="5">
         <v>372375</v>
@@ -1715,14 +1715,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>107245</v>
+        <v>107302</v>
       </c>
       <c r="P12" s="5">
-        <v>371417</v>
+        <v>371474</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99742732460557237</v>
+        <v>0.99758039610607585</v>
       </c>
       <c r="R12" s="5">
         <v>184659</v>
@@ -1732,14 +1732,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>40620</v>
+        <v>40652</v>
       </c>
       <c r="U12" s="5">
-        <v>183359</v>
+        <v>183391</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99295999653415212</v>
+        <v>0.99313328892715758</v>
       </c>
       <c r="W12" s="5">
         <v>189081</v>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>40798</v>
+        <v>40839</v>
       </c>
       <c r="Z12" s="5">
-        <v>185603</v>
+        <v>185644</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.98160576684066614</v>
+        <v>0.98182260512690334</v>
       </c>
       <c r="AB12" s="5">
         <v>377441</v>
@@ -1766,14 +1766,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>113830</v>
+        <v>113945</v>
       </c>
       <c r="AE12" s="5">
-        <v>374922</v>
+        <v>375037</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99332610924621334</v>
+        <v>0.99363079262719212</v>
       </c>
       <c r="AG12" s="5">
         <v>186148</v>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>42034</v>
+        <v>42104</v>
       </c>
       <c r="AJ12" s="5">
-        <v>184742</v>
+        <v>184812</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.99244687023228828</v>
+        <v>0.99282291509981302</v>
       </c>
       <c r="AL12" s="5">
         <v>192239</v>
@@ -1800,14 +1800,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>41451</v>
+        <v>41555</v>
       </c>
       <c r="AO12" s="5">
-        <v>191096</v>
+        <v>191200</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.99405427618745412</v>
+        <v>0.99459526943024046</v>
       </c>
       <c r="AQ12" s="5">
         <v>384779</v>
@@ -1817,14 +1817,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>112939</v>
+        <v>113241</v>
       </c>
       <c r="AT12" s="5">
-        <v>384328</v>
+        <v>384630</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99882789861193044</v>
+        <v>0.99961276472988392</v>
       </c>
       <c r="AV12" s="5">
         <v>191743</v>
@@ -1834,14 +1834,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>25540</v>
+        <v>25820</v>
       </c>
       <c r="AY12" s="5">
-        <v>191045</v>
+        <v>191325</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99635971065436546</v>
+        <v>0.99781999864401827</v>
       </c>
       <c r="BA12" s="5">
         <v>197493</v>
@@ -1851,14 +1851,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>40968</v>
+        <v>41393</v>
       </c>
       <c r="BD12" s="5">
-        <v>194627</v>
+        <v>195052</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98548809324887465</v>
+        <v>0.9876400682555837</v>
       </c>
       <c r="BF12" s="5">
         <v>393305</v>
@@ -1868,14 +1868,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>112573</v>
+        <v>114140</v>
       </c>
       <c r="BI12" s="5">
-        <v>389162</v>
+        <v>390729</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.98946619036117012</v>
+        <v>0.99345037566265371</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1893,14 +1893,14 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>3916</v>
+        <v>3919</v>
       </c>
       <c r="F13" s="5">
-        <v>17990</v>
+        <v>17993</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>0.99750485167729419</v>
+        <v>0.99767119489880784</v>
       </c>
       <c r="H13" s="5">
         <v>18257</v>
@@ -1910,14 +1910,14 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="2"/>
-        <v>3773</v>
+        <v>3776</v>
       </c>
       <c r="K13" s="5">
-        <v>18075</v>
+        <v>18078</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" si="3"/>
-        <v>0.99003122090157203</v>
+        <v>0.99019554143616151</v>
       </c>
       <c r="M13" s="5">
         <v>29011</v>
@@ -1927,14 +1927,14 @@
       </c>
       <c r="O13" s="3">
         <f t="shared" si="4"/>
-        <v>7195</v>
+        <v>7200</v>
       </c>
       <c r="P13" s="5">
-        <v>29046</v>
+        <v>29051</v>
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="5"/>
-        <v>1.001206438936955</v>
+        <v>1.0013787873565199</v>
       </c>
       <c r="R13" s="5">
         <v>18140</v>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="T13" s="3">
         <f t="shared" si="6"/>
-        <v>3741</v>
+        <v>3744</v>
       </c>
       <c r="U13" s="5">
-        <v>18131</v>
+        <v>18134</v>
       </c>
       <c r="V13" s="4">
         <f t="shared" si="7"/>
-        <v>0.99950385887541349</v>
+        <v>0.99966923925027562</v>
       </c>
       <c r="W13" s="5">
         <v>18401</v>
@@ -1961,14 +1961,14 @@
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="8"/>
-        <v>3491</v>
+        <v>3495</v>
       </c>
       <c r="Z13" s="5">
-        <v>18239</v>
+        <v>18243</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="9"/>
-        <v>0.99119613064507361</v>
+        <v>0.99141351013531875</v>
       </c>
       <c r="AB13" s="5">
         <v>29242</v>
@@ -1978,14 +1978,14 @@
       </c>
       <c r="AD13" s="3">
         <f t="shared" si="10"/>
-        <v>7561</v>
+        <v>7570</v>
       </c>
       <c r="AE13" s="5">
-        <v>29283</v>
+        <v>29292</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="11"/>
-        <v>1.001402092880104</v>
+        <v>1.0017098693659805</v>
       </c>
       <c r="AG13" s="5">
         <v>18261</v>
@@ -1995,14 +1995,14 @@
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="12"/>
-        <v>3798</v>
+        <v>3807</v>
       </c>
       <c r="AJ13" s="5">
-        <v>18392</v>
+        <v>18401</v>
       </c>
       <c r="AK13" s="4">
         <f t="shared" si="13"/>
-        <v>1.007173758282679</v>
+        <v>1.0076666119051532</v>
       </c>
       <c r="AL13" s="5">
         <v>18637</v>
@@ -2012,14 +2012,14 @@
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="14"/>
-        <v>3673</v>
+        <v>3683</v>
       </c>
       <c r="AO13" s="5">
-        <v>18736</v>
+        <v>18746</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="15"/>
-        <v>1.0053120137361162</v>
+        <v>1.0058485807801685</v>
       </c>
       <c r="AQ13" s="5">
         <v>29668</v>
@@ -2029,14 +2029,14 @@
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="16"/>
-        <v>7475</v>
+        <v>7503</v>
       </c>
       <c r="AT13" s="5">
-        <v>29866</v>
+        <v>29894</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="17"/>
-        <v>1.0066738573547256</v>
+        <v>1.0076176351624646</v>
       </c>
       <c r="AV13" s="5">
         <v>18676</v>
@@ -2046,14 +2046,14 @@
       </c>
       <c r="AX13" s="3">
         <f t="shared" si="18"/>
-        <v>2495</v>
+        <v>2525</v>
       </c>
       <c r="AY13" s="5">
-        <v>18866</v>
+        <v>18896</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="19"/>
-        <v>1.0101734846862283</v>
+        <v>1.0117798243735274</v>
       </c>
       <c r="BA13" s="5">
         <v>19025</v>
@@ -2063,14 +2063,14 @@
       </c>
       <c r="BC13" s="3">
         <f t="shared" si="20"/>
-        <v>3616</v>
+        <v>3662</v>
       </c>
       <c r="BD13" s="5">
-        <v>19131</v>
+        <v>19177</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="21"/>
-        <v>1.0055716162943495</v>
+        <v>1.0079894875164257</v>
       </c>
       <c r="BF13" s="5">
         <v>30254</v>
@@ -2080,14 +2080,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>7294</v>
+        <v>7423</v>
       </c>
       <c r="BI13" s="5">
-        <v>30170</v>
+        <v>30299</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>0.99722350763535406</v>
+        <v>1.0014874066239174</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2105,14 +2105,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>42279</v>
+        <v>42308</v>
       </c>
       <c r="F14" s="5">
-        <v>95183</v>
+        <v>95212</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>1.0060245420819549</v>
+        <v>1.0063310538720895</v>
       </c>
       <c r="H14" s="5">
         <v>97351</v>
@@ -2122,14 +2122,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>43547</v>
+        <v>43579</v>
       </c>
       <c r="K14" s="5">
-        <v>97167</v>
+        <v>97199</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.99810993210136512</v>
+        <v>0.9984386395619973</v>
       </c>
       <c r="M14" s="5">
         <v>172809</v>
@@ -2139,14 +2139,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>88216</v>
+        <v>88280</v>
       </c>
       <c r="P14" s="5">
-        <v>173001</v>
+        <v>173065</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>1.0011110532437546</v>
+        <v>1.0014814043250062</v>
       </c>
       <c r="R14" s="5">
         <v>97326</v>
@@ -2156,14 +2156,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>41905</v>
+        <v>41948</v>
       </c>
       <c r="U14" s="5">
-        <v>96429</v>
+        <v>96472</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.99078355218543868</v>
+        <v>0.9912253662947208</v>
       </c>
       <c r="W14" s="5">
         <v>98912</v>
@@ -2173,14 +2173,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>41365</v>
+        <v>41416</v>
       </c>
       <c r="Z14" s="5">
-        <v>97741</v>
+        <v>97792</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.98816119378841794</v>
+        <v>0.98867680362342281</v>
       </c>
       <c r="AB14" s="5">
         <v>175426</v>
@@ -2190,14 +2190,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>91629</v>
+        <v>91735</v>
       </c>
       <c r="AE14" s="5">
-        <v>175646</v>
+        <v>175752</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>1.0012540900436651</v>
+        <v>1.0018583334283402</v>
       </c>
       <c r="AG14" s="5">
         <v>98057</v>
@@ -2207,14 +2207,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>42681</v>
+        <v>42758</v>
       </c>
       <c r="AJ14" s="5">
-        <v>98026</v>
+        <v>98103</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99968385734827703</v>
+        <v>1.0004691149025566</v>
       </c>
       <c r="AL14" s="5">
         <v>101581</v>
@@ -2224,14 +2224,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>43789</v>
+        <v>43905</v>
       </c>
       <c r="AO14" s="5">
-        <v>102495</v>
+        <v>102611</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>1.0089977456414094</v>
+        <v>1.010139691477737</v>
       </c>
       <c r="AQ14" s="5">
         <v>182247</v>
@@ -2241,14 +2241,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>93084</v>
+        <v>93327</v>
       </c>
       <c r="AT14" s="5">
-        <v>182853</v>
+        <v>183096</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>1.0033251576157631</v>
+        <v>1.0046585128973315</v>
       </c>
       <c r="AV14" s="5">
         <v>102257</v>
@@ -2258,14 +2258,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>17515</v>
+        <v>17731</v>
       </c>
       <c r="AY14" s="5">
-        <v>103023</v>
+        <v>103239</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>1.0074909297163031</v>
+        <v>1.0096032545449212</v>
       </c>
       <c r="BA14" s="5">
         <v>106311</v>
@@ -2275,14 +2275,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>44767</v>
+        <v>45061</v>
       </c>
       <c r="BD14" s="5">
-        <v>105503</v>
+        <v>105797</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.99239965760833782</v>
+        <v>0.99516512872609608</v>
       </c>
       <c r="BF14" s="5">
         <v>189210</v>
@@ -2292,14 +2292,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>94336</v>
+        <v>95299</v>
       </c>
       <c r="BI14" s="5">
-        <v>187187</v>
+        <v>188150</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.98930817610062893</v>
+        <v>0.99439775910364148</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2317,14 +2317,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>85899</v>
+        <v>85922</v>
       </c>
       <c r="F15" s="5">
-        <v>323681</v>
+        <v>323704</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.99656707594921123</v>
+        <v>0.99663788962918265</v>
       </c>
       <c r="H15" s="5">
         <v>331968</v>
@@ -2334,14 +2334,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>85272</v>
+        <v>85296</v>
       </c>
       <c r="K15" s="5">
-        <v>329334</v>
+        <v>329358</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.9920655002891845</v>
+        <v>0.99213779641411215</v>
       </c>
       <c r="M15" s="5">
         <v>549212</v>
@@ -2351,14 +2351,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>165589</v>
+        <v>165644</v>
       </c>
       <c r="P15" s="5">
-        <v>548509</v>
+        <v>548564</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99871998426836994</v>
+        <v>0.99882012774666251</v>
       </c>
       <c r="R15" s="5">
         <v>333160</v>
@@ -2368,14 +2368,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>84527</v>
+        <v>84569</v>
       </c>
       <c r="U15" s="5">
-        <v>331755</v>
+        <v>331797</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99578280705967104</v>
+        <v>0.99590887261375916</v>
       </c>
       <c r="W15" s="5">
         <v>340519</v>
@@ -2385,14 +2385,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>82422</v>
+        <v>82476</v>
       </c>
       <c r="Z15" s="5">
-        <v>336728</v>
+        <v>336782</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98886699420590329</v>
+        <v>0.98902557566538141</v>
       </c>
       <c r="AB15" s="5">
         <v>562036</v>
@@ -2402,14 +2402,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>176360</v>
+        <v>176467</v>
       </c>
       <c r="AE15" s="5">
-        <v>559606</v>
+        <v>559713</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99567643353806523</v>
+        <v>0.99586681280202694</v>
       </c>
       <c r="AG15" s="5">
         <v>340264</v>
@@ -2419,14 +2419,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>87933</v>
+        <v>88027</v>
       </c>
       <c r="AJ15" s="5">
-        <v>338827</v>
+        <v>338921</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99577680859567863</v>
+        <v>0.9960530646791903</v>
       </c>
       <c r="AL15" s="5">
         <v>350627</v>
@@ -2436,14 +2436,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>88876</v>
+        <v>89002</v>
       </c>
       <c r="AO15" s="5">
-        <v>352260</v>
+        <v>352386</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>1.0046573709383475</v>
+        <v>1.0050167271773138</v>
       </c>
       <c r="AQ15" s="5">
         <v>580651</v>
@@ -2453,14 +2453,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>177366</v>
+        <v>177746</v>
       </c>
       <c r="AT15" s="5">
-        <v>582555</v>
+        <v>582935</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>1.0032790781381586</v>
+        <v>1.003933516001867</v>
       </c>
       <c r="AV15" s="5">
         <v>355536</v>
@@ -2470,14 +2470,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>51270</v>
+        <v>51700</v>
       </c>
       <c r="AY15" s="5">
-        <v>356290</v>
+        <v>356720</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>1.0021207416407902</v>
+        <v>1.0033301831600738</v>
       </c>
       <c r="BA15" s="5">
         <v>365201</v>
@@ -2487,14 +2487,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>89167</v>
+        <v>89909</v>
       </c>
       <c r="BD15" s="5">
-        <v>363503</v>
+        <v>364245</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.99535050561197802</v>
+        <v>0.99738226346587222</v>
       </c>
       <c r="BF15" s="5">
         <v>600313</v>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>178185</v>
+        <v>180403</v>
       </c>
       <c r="BI15" s="5">
-        <v>595783</v>
+        <v>598001</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99245393652977698</v>
+        <v>0.99614867577413779</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2529,14 +2529,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>119624</v>
+        <v>119706</v>
       </c>
       <c r="F16" s="5">
-        <v>450930</v>
+        <v>451012</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99429350102972758</v>
+        <v>0.99447430972971307</v>
       </c>
       <c r="H16" s="5">
         <v>461360</v>
@@ -2546,14 +2546,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>119968</v>
+        <v>120053</v>
       </c>
       <c r="K16" s="5">
-        <v>458588</v>
+        <v>458673</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.99399167678168887</v>
+        <v>0.99417591468701227</v>
       </c>
       <c r="M16" s="5">
         <v>788355</v>
@@ -2563,14 +2563,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>217565</v>
+        <v>217754</v>
       </c>
       <c r="P16" s="5">
-        <v>789548</v>
+        <v>789737</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>1.0015132776477602</v>
+        <v>1.0017530173589309</v>
       </c>
       <c r="R16" s="5">
         <v>462019</v>
@@ -2580,14 +2580,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>120187</v>
+        <v>120303</v>
       </c>
       <c r="U16" s="5">
-        <v>461718</v>
+        <v>461834</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99934851164129612</v>
+        <v>0.99959958356690959</v>
       </c>
       <c r="W16" s="5">
         <v>472236</v>
@@ -2597,14 +2597,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>116086</v>
+        <v>116229</v>
       </c>
       <c r="Z16" s="5">
-        <v>467167</v>
+        <v>467310</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98926596024021884</v>
+        <v>0.98956877493456663</v>
       </c>
       <c r="AB16" s="5">
         <v>804216</v>
@@ -2614,14 +2614,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>232863</v>
+        <v>233189</v>
       </c>
       <c r="AE16" s="5">
-        <v>802025</v>
+        <v>802351</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99727560754822087</v>
+        <v>0.99768097128134725</v>
       </c>
       <c r="AG16" s="5">
         <v>471201</v>
@@ -2631,14 +2631,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>122395</v>
+        <v>122612</v>
       </c>
       <c r="AJ16" s="5">
-        <v>469287</v>
+        <v>469504</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.99593803918073176</v>
+        <v>0.99639856451917552</v>
       </c>
       <c r="AL16" s="5">
         <v>484445</v>
@@ -2648,14 +2648,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>127941</v>
+        <v>128220</v>
       </c>
       <c r="AO16" s="5">
-        <v>489456</v>
+        <v>489735</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>1.0103437954772987</v>
+        <v>1.0109197122480365</v>
       </c>
       <c r="AQ16" s="5">
         <v>831010</v>
@@ -2665,14 +2665,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>237679</v>
+        <v>238428</v>
       </c>
       <c r="AT16" s="5">
-        <v>834675</v>
+        <v>835424</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>1.004410295904983</v>
+        <v>1.0053116087652374</v>
       </c>
       <c r="AV16" s="5">
         <v>496237</v>
@@ -2682,14 +2682,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>73869</v>
+        <v>74667</v>
       </c>
       <c r="AY16" s="5">
-        <v>496737</v>
+        <v>497535</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>1.0010075830701861</v>
+        <v>1.0026156856502035</v>
       </c>
       <c r="BA16" s="5">
         <v>510690</v>
@@ -2699,14 +2699,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>126463</v>
+        <v>127681</v>
       </c>
       <c r="BD16" s="5">
-        <v>506051</v>
+        <v>507269</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.99091621140026243</v>
+        <v>0.9933012199181499</v>
       </c>
       <c r="BF16" s="5">
         <v>859721</v>
@@ -2716,14 +2716,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>234764</v>
+        <v>237993</v>
       </c>
       <c r="BI16" s="5">
-        <v>851700</v>
+        <v>854929</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99067022906268432</v>
+        <v>0.99442609869946175</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>106475</v>
+        <v>106516</v>
       </c>
       <c r="F17" s="5">
-        <v>339560</v>
+        <v>339601</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99211415916016821</v>
+        <v>0.9922339514811882</v>
       </c>
       <c r="H17" s="5">
         <v>352243</v>
@@ -2758,14 +2758,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>105212</v>
+        <v>105268</v>
       </c>
       <c r="K17" s="5">
-        <v>347598</v>
+        <v>347654</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98681308074255558</v>
+        <v>0.98697206190044939</v>
       </c>
       <c r="M17" s="5">
         <v>765449</v>
@@ -2775,14 +2775,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>302953</v>
+        <v>303107</v>
       </c>
       <c r="P17" s="5">
-        <v>765903</v>
+        <v>766057</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>1.0005931159358756</v>
+        <v>1.0007943050418773</v>
       </c>
       <c r="R17" s="5">
         <v>346814</v>
@@ -2792,14 +2792,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>103934</v>
+        <v>104017</v>
       </c>
       <c r="U17" s="5">
-        <v>346982</v>
+        <v>347065</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>1.0004844095105734</v>
+        <v>1.0007237308759163</v>
       </c>
       <c r="W17" s="5">
         <v>360071</v>
@@ -2809,14 +2809,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>105503</v>
+        <v>105601</v>
       </c>
       <c r="Z17" s="5">
-        <v>355755</v>
+        <v>355853</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.98801347512018467</v>
+        <v>0.98828564366472171</v>
       </c>
       <c r="AB17" s="5">
         <v>784641</v>
@@ -2826,14 +2826,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>317878</v>
+        <v>318175</v>
       </c>
       <c r="AE17" s="5">
-        <v>784479</v>
+        <v>784776</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99979353615220212</v>
+        <v>1.0001720532064982</v>
       </c>
       <c r="AG17" s="5">
         <v>355351</v>
@@ -2843,14 +2843,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>110331</v>
+        <v>110494</v>
       </c>
       <c r="AJ17" s="5">
-        <v>355483</v>
+        <v>355646</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>1.0003714637077143</v>
+        <v>1.0008301651043616</v>
       </c>
       <c r="AL17" s="5">
         <v>371770</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>112062</v>
+        <v>112290</v>
       </c>
       <c r="AO17" s="5">
-        <v>371851</v>
+        <v>372079</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>1.0002178766441616</v>
+        <v>1.0008311590499503</v>
       </c>
       <c r="AQ17" s="5">
         <v>810773</v>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>316626</v>
+        <v>317409</v>
       </c>
       <c r="AT17" s="5">
-        <v>813351</v>
+        <v>814134</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>1.0031796816124858</v>
+        <v>1.004145426648396</v>
       </c>
       <c r="AV17" s="5">
         <v>369648</v>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>53473</v>
+        <v>54040</v>
       </c>
       <c r="AY17" s="5">
-        <v>370904</v>
+        <v>371471</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>1.0033978271220187</v>
+        <v>1.0049317188243951</v>
       </c>
       <c r="BA17" s="5">
         <v>385393</v>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>114190</v>
+        <v>115014</v>
       </c>
       <c r="BD17" s="5">
-        <v>382701</v>
+        <v>383525</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.99301492242983136</v>
+        <v>0.99515299966527671</v>
       </c>
       <c r="BF17" s="5">
         <v>839843</v>
@@ -2928,14 +2928,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>327664</v>
+        <v>331634</v>
       </c>
       <c r="BI17" s="5">
-        <v>831318</v>
+        <v>835288</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.98984929326076421</v>
+        <v>0.99457636724959309</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>542506</v>
+        <v>542658</v>
       </c>
       <c r="F18" s="5">
-        <v>1062958</v>
+        <v>1063110</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.99262459191525287</v>
+        <v>0.9927665344360026</v>
       </c>
       <c r="H18" s="5">
         <v>1089051</v>
@@ -2970,14 +2970,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>555686</v>
+        <v>555865</v>
       </c>
       <c r="K18" s="5">
-        <v>1079627</v>
+        <v>1079806</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.99134659442027973</v>
+        <v>0.99151095770537834</v>
       </c>
       <c r="M18" s="5">
         <v>1637429</v>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>875848</v>
+        <v>876165</v>
       </c>
       <c r="P18" s="5">
-        <v>1628636</v>
+        <v>1628953</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99462999617082637</v>
+        <v>0.99482359235117979</v>
       </c>
       <c r="R18" s="5">
         <v>1090030</v>
@@ -3004,14 +3004,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>545459</v>
+        <v>545708</v>
       </c>
       <c r="U18" s="5">
-        <v>1078520</v>
+        <v>1078769</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98944065759657995</v>
+        <v>0.98966909167637584</v>
       </c>
       <c r="W18" s="5">
         <v>1107435</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>539007</v>
+        <v>539321</v>
       </c>
       <c r="Z18" s="5">
-        <v>1090013</v>
+        <v>1090327</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.98426815117817301</v>
+        <v>0.98455168926392966</v>
       </c>
       <c r="AB18" s="5">
         <v>1665905</v>
@@ -3038,14 +3038,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>905486</v>
+        <v>906158</v>
       </c>
       <c r="AE18" s="5">
-        <v>1652284</v>
+        <v>1652956</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.99182366341418027</v>
+        <v>0.99222704776082671</v>
       </c>
       <c r="AG18" s="5">
         <v>1104366</v>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>555707</v>
+        <v>556244</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1094514</v>
+        <v>1095051</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99107904444722128</v>
+        <v>0.99156529628764378</v>
       </c>
       <c r="AL18" s="5">
         <v>1131950</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>565756</v>
+        <v>566520</v>
       </c>
       <c r="AO18" s="5">
-        <v>1133761</v>
+        <v>1134525</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>1.0015998939882504</v>
+        <v>1.0022748354609303</v>
       </c>
       <c r="AQ18" s="5">
         <v>1717059</v>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>923928</v>
+        <v>925725</v>
       </c>
       <c r="AT18" s="5">
-        <v>1715886</v>
+        <v>1717683</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99931685515756885</v>
+        <v>1.0003634120900913</v>
       </c>
       <c r="AV18" s="5">
         <v>1151692</v>
@@ -3106,14 +3106,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>184247</v>
+        <v>186069</v>
       </c>
       <c r="AY18" s="5">
-        <v>1149764</v>
+        <v>1151586</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99832594131069763</v>
+        <v>0.9999079615035964</v>
       </c>
       <c r="BA18" s="5">
         <v>1182353</v>
@@ -3123,14 +3123,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>582547</v>
+        <v>585300</v>
       </c>
       <c r="BD18" s="5">
-        <v>1171110</v>
+        <v>1173863</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.99049099549796038</v>
+        <v>0.99281940334231822</v>
       </c>
       <c r="BF18" s="5">
         <v>1777125</v>
@@ -3140,14 +3140,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>934936</v>
+        <v>942506</v>
       </c>
       <c r="BI18" s="5">
-        <v>1751941</v>
+        <v>1759511</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.98582879651121891</v>
+        <v>0.99008848561581209</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3165,14 +3165,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>178511</v>
+        <v>178605</v>
       </c>
       <c r="F19" s="5">
-        <v>299505</v>
+        <v>299599</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.97999469928243987</v>
+        <v>0.98030227178284068</v>
       </c>
       <c r="H19" s="5">
         <v>314567</v>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>183982</v>
+        <v>184096</v>
       </c>
       <c r="K19" s="5">
-        <v>306490</v>
+        <v>306604</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.97432343507106589</v>
+        <v>0.97468583799317787</v>
       </c>
       <c r="M19" s="5">
         <v>534704</v>
@@ -3199,14 +3199,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>333776</v>
+        <v>334037</v>
       </c>
       <c r="P19" s="5">
-        <v>527941</v>
+        <v>528202</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98735188066668667</v>
+        <v>0.98784000119692394</v>
       </c>
       <c r="R19" s="5">
         <v>310887</v>
@@ -3216,14 +3216,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>179669</v>
+        <v>179839</v>
       </c>
       <c r="U19" s="5">
-        <v>305538</v>
+        <v>305708</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.98279439153132808</v>
+        <v>0.98334121401023522</v>
       </c>
       <c r="W19" s="5">
         <v>321022</v>
@@ -3233,14 +3233,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>179687</v>
+        <v>179886</v>
       </c>
       <c r="Z19" s="5">
-        <v>310742</v>
+        <v>310941</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.96797727258567945</v>
+        <v>0.96859716779535354</v>
       </c>
       <c r="AB19" s="5">
         <v>548160</v>
@@ -3250,14 +3250,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>351787</v>
+        <v>352293</v>
       </c>
       <c r="AE19" s="5">
-        <v>538177</v>
+        <v>538683</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.98178816403969649</v>
+        <v>0.9827112521891419</v>
       </c>
       <c r="AG19" s="5">
         <v>315587</v>
@@ -3267,14 +3267,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>189394</v>
+        <v>189712</v>
       </c>
       <c r="AJ19" s="5">
-        <v>309469</v>
+        <v>309787</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.98061390361453415</v>
+        <v>0.98162154968360549</v>
       </c>
       <c r="AL19" s="5">
         <v>327315</v>
@@ -3284,14 +3284,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>189319</v>
+        <v>189747</v>
       </c>
       <c r="AO19" s="5">
-        <v>322413</v>
+        <v>322841</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.98502360111818887</v>
+        <v>0.9863312099964866</v>
       </c>
       <c r="AQ19" s="5">
         <v>564697</v>
@@ -3301,14 +3301,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>358554</v>
+        <v>359740</v>
       </c>
       <c r="AT19" s="5">
-        <v>560889</v>
+        <v>562075</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.99325656059798439</v>
+        <v>0.99535680196636422</v>
       </c>
       <c r="AV19" s="5">
         <v>330794</v>
@@ -3318,14 +3318,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>60463</v>
+        <v>61502</v>
       </c>
       <c r="AY19" s="5">
-        <v>328588</v>
+        <v>329627</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.99333119705919692</v>
+        <v>0.99647212464554979</v>
       </c>
       <c r="BA19" s="5">
         <v>346688</v>
@@ -3335,14 +3335,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>199290</v>
+        <v>200828</v>
       </c>
       <c r="BD19" s="5">
-        <v>338249</v>
+        <v>339787</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.97565822872438623</v>
+        <v>0.98009449418497319</v>
       </c>
       <c r="BF19" s="5">
         <v>595475</v>
@@ -3352,14 +3352,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>376194</v>
+        <v>381180</v>
       </c>
       <c r="BI19" s="5">
-        <v>575764</v>
+        <v>580750</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.9668986943196608</v>
+        <v>0.9752718418069608</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3377,14 +3377,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3892</v>
+        <v>3894</v>
       </c>
       <c r="F20" s="5">
-        <v>6479</v>
+        <v>6481</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.99112742848401403</v>
+        <v>0.99143337922594466</v>
       </c>
       <c r="H20" s="5">
         <v>6601</v>
@@ -3394,14 +3394,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3842</v>
+        <v>3844</v>
       </c>
       <c r="K20" s="5">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.98651719436449026</v>
+        <v>0.98682017876079386</v>
       </c>
       <c r="M20" s="5">
         <v>10050</v>
@@ -3411,14 +3411,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5572</v>
+        <v>5577</v>
       </c>
       <c r="P20" s="5">
-        <v>10040</v>
+        <v>10045</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.99900497512437814</v>
+        <v>0.99950248756218907</v>
       </c>
       <c r="R20" s="5">
         <v>6485</v>
@@ -3428,14 +3428,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3630</v>
+        <v>3632</v>
       </c>
       <c r="U20" s="5">
-        <v>6434</v>
+        <v>6436</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>0.99213569776407096</v>
+        <v>0.9924441017733231</v>
       </c>
       <c r="W20" s="5">
         <v>6573</v>
@@ -3445,14 +3445,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>3441</v>
+        <v>3444</v>
       </c>
       <c r="Z20" s="5">
-        <v>6449</v>
+        <v>6452</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>0.98113494599117601</v>
+        <v>0.98159135858816371</v>
       </c>
       <c r="AB20" s="5">
         <v>10123</v>
@@ -3462,14 +3462,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>6159</v>
+        <v>6166</v>
       </c>
       <c r="AE20" s="5">
-        <v>10055</v>
+        <v>10062</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>0.9932826237281438</v>
+        <v>0.99397411834436433</v>
       </c>
       <c r="AG20" s="5">
         <v>6547</v>
@@ -3479,14 +3479,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3448</v>
+        <v>3453</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6466</v>
+        <v>6471</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>0.98762792118527565</v>
+        <v>0.98839162975408579</v>
       </c>
       <c r="AL20" s="5">
         <v>6649</v>
@@ -3496,14 +3496,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3461</v>
+        <v>3467</v>
       </c>
       <c r="AO20" s="5">
-        <v>6552</v>
+        <v>6558</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.98541134005113551</v>
+        <v>0.98631373138817868</v>
       </c>
       <c r="AQ20" s="5">
         <v>10228</v>
@@ -3513,14 +3513,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>6141</v>
+        <v>6175</v>
       </c>
       <c r="AT20" s="5">
-        <v>10137</v>
+        <v>10171</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>0.99110285490809547</v>
+        <v>0.99442706296441141</v>
       </c>
       <c r="AV20" s="5">
         <v>6568</v>
@@ -3530,14 +3530,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>1394</v>
+        <v>1416</v>
       </c>
       <c r="AY20" s="5">
-        <v>6478</v>
+        <v>6500</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.98629719853836784</v>
+        <v>0.989646772228989</v>
       </c>
       <c r="BA20" s="5">
         <v>6793</v>
@@ -3547,14 +3547,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3330</v>
+        <v>3362</v>
       </c>
       <c r="BD20" s="5">
-        <v>6528</v>
+        <v>6560</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.96098925364345655</v>
+        <v>0.96569998527896361</v>
       </c>
       <c r="BF20" s="5">
         <v>10395</v>
@@ -3564,14 +3564,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>5894</v>
+        <v>5992</v>
       </c>
       <c r="BI20" s="5">
-        <v>10102</v>
+        <v>10200</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>0.9718133718133718</v>
+        <v>0.98124098124098125</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>9108</v>
+        <v>9121</v>
       </c>
       <c r="F21" s="5">
-        <v>12078</v>
+        <v>12091</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>1.0056619483763531</v>
+        <v>1.0067443796835971</v>
       </c>
       <c r="H21" s="5">
         <v>12254</v>
@@ -3606,14 +3606,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>9076</v>
+        <v>9093</v>
       </c>
       <c r="K21" s="5">
-        <v>12300</v>
+        <v>12317</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>1.0037538762852947</v>
+        <v>1.0051411783907296</v>
       </c>
       <c r="M21" s="5">
         <v>16207</v>
@@ -3623,14 +3623,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>12169</v>
+        <v>12195</v>
       </c>
       <c r="P21" s="5">
-        <v>16436</v>
+        <v>16462</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0141296970444869</v>
+        <v>1.0157339421237737</v>
       </c>
       <c r="R21" s="5">
         <v>12383</v>
@@ -3640,14 +3640,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>9170</v>
+        <v>9192</v>
       </c>
       <c r="U21" s="5">
-        <v>12589</v>
+        <v>12611</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0166357102479204</v>
+        <v>1.0184123394976985</v>
       </c>
       <c r="W21" s="5">
         <v>12782</v>
@@ -3657,14 +3657,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>9199</v>
+        <v>9221</v>
       </c>
       <c r="Z21" s="5">
-        <v>12800</v>
+        <v>12822</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0014082303238929</v>
+        <v>1.0031294007197622</v>
       </c>
       <c r="AB21" s="5">
         <v>16816</v>
@@ -3674,14 +3674,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>12692</v>
+        <v>12730</v>
       </c>
       <c r="AE21" s="5">
-        <v>16901</v>
+        <v>16939</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0050547098001903</v>
+        <v>1.007314462416746</v>
       </c>
       <c r="AG21" s="5">
         <v>12696</v>
@@ -3691,14 +3691,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>9340</v>
+        <v>9372</v>
       </c>
       <c r="AJ21" s="5">
-        <v>12782</v>
+        <v>12814</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0067737870195337</v>
+        <v>1.0092942659105231</v>
       </c>
       <c r="AL21" s="5">
         <v>13072</v>
@@ -3708,14 +3708,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>9378</v>
+        <v>9423</v>
       </c>
       <c r="AO21" s="5">
-        <v>13029</v>
+        <v>13074</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>0.99671052631578949</v>
+        <v>1.0001529987760098</v>
       </c>
       <c r="AQ21" s="5">
         <v>17310</v>
@@ -3725,14 +3725,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>12832</v>
+        <v>12917</v>
       </c>
       <c r="AT21" s="5">
-        <v>17311</v>
+        <v>17396</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.000057770075101</v>
+        <v>1.0049682264586943</v>
       </c>
       <c r="AV21" s="5">
         <v>13094</v>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>3526</v>
+        <v>3619</v>
       </c>
       <c r="AY21" s="5">
-        <v>13015</v>
+        <v>13108</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>0.99396670230639983</v>
+        <v>1.0010691919963342</v>
       </c>
       <c r="BA21" s="5">
         <v>13518</v>
@@ -3759,14 +3759,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>9017</v>
+        <v>9144</v>
       </c>
       <c r="BD21" s="5">
-        <v>13165</v>
+        <v>13292</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>0.97388666962568426</v>
+        <v>0.98328155052522559</v>
       </c>
       <c r="BF21" s="5">
         <v>17905</v>
@@ -3776,14 +3776,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>12274</v>
+        <v>12623</v>
       </c>
       <c r="BI21" s="5">
-        <v>16882</v>
+        <v>17231</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>0.94286512147444845</v>
+        <v>0.96235688355208038</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4878</v>
+        <v>4886</v>
       </c>
       <c r="F22" s="5">
-        <v>6991</v>
+        <v>6999</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.99928530588907949</v>
+        <v>1.0004288164665522</v>
       </c>
       <c r="H22" s="5">
         <v>7077</v>
@@ -3818,14 +3818,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4832</v>
+        <v>4840</v>
       </c>
       <c r="K22" s="5">
-        <v>7052</v>
+        <v>7060</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>0.99646742970185109</v>
+        <v>0.99759785219725872</v>
       </c>
       <c r="M22" s="5">
         <v>8504</v>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5771</v>
+        <v>5781</v>
       </c>
       <c r="P22" s="5">
-        <v>8547</v>
+        <v>8557</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0050564440263405</v>
+        <v>1.0062323612417685</v>
       </c>
       <c r="R22" s="5">
         <v>7111</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4654</v>
+        <v>4662</v>
       </c>
       <c r="U22" s="5">
-        <v>7094</v>
+        <v>7102</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>0.99760933764590076</v>
+        <v>0.99873435522430043</v>
       </c>
       <c r="W22" s="5">
         <v>7191</v>
@@ -3869,14 +3869,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4651</v>
+        <v>4659</v>
       </c>
       <c r="Z22" s="5">
-        <v>7160</v>
+        <v>7168</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.99568905576414968</v>
+        <v>0.9968015575024336</v>
       </c>
       <c r="AB22" s="5">
         <v>8707</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5916</v>
+        <v>5927</v>
       </c>
       <c r="AE22" s="5">
-        <v>8692</v>
+        <v>8703</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>0.99827724819111063</v>
+        <v>0.99954059951762952</v>
       </c>
       <c r="AG22" s="5">
         <v>7162</v>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4706</v>
+        <v>4717</v>
       </c>
       <c r="AJ22" s="5">
-        <v>7159</v>
+        <v>7170</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>0.99958112259145493</v>
+        <v>1.001117006422787</v>
       </c>
       <c r="AL22" s="5">
         <v>7226</v>
@@ -3920,14 +3920,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4699</v>
+        <v>4713</v>
       </c>
       <c r="AO22" s="5">
-        <v>7213</v>
+        <v>7227</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>0.99820094104622192</v>
+        <v>1.0001383891502906</v>
       </c>
       <c r="AQ22" s="5">
         <v>8754</v>
@@ -3937,14 +3937,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>6143</v>
+        <v>6169</v>
       </c>
       <c r="AT22" s="5">
-        <v>8755</v>
+        <v>8781</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0001142334932602</v>
+        <v>1.003084304318026</v>
       </c>
       <c r="AV22" s="5">
         <v>7182</v>
@@ -3954,14 +3954,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>1768</v>
+        <v>1795</v>
       </c>
       <c r="AY22" s="5">
-        <v>7154</v>
+        <v>7181</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.99610136452241715</v>
+        <v>0.99986076301865778</v>
       </c>
       <c r="BA22" s="5">
         <v>7296</v>
@@ -3971,14 +3971,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4627</v>
+        <v>4668</v>
       </c>
       <c r="BD22" s="5">
-        <v>7195</v>
+        <v>7236</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.98615679824561409</v>
+        <v>0.99177631578947367</v>
       </c>
       <c r="BF22" s="5">
         <v>8939</v>
@@ -3988,14 +3988,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5803</v>
+        <v>5898</v>
       </c>
       <c r="BI22" s="5">
-        <v>8625</v>
+        <v>8720</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>0.96487302830294219</v>
+        <v>0.97550061528135135</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4013,14 +4013,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6682</v>
+        <v>6693</v>
       </c>
       <c r="F23" s="5">
-        <v>9210</v>
+        <v>9221</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.97905814818751991</v>
+        <v>0.98022749016689703</v>
       </c>
       <c r="H23" s="5">
         <v>9786</v>
@@ -4030,14 +4030,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7355</v>
+        <v>7366</v>
       </c>
       <c r="K23" s="5">
-        <v>9352</v>
+        <v>9363</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.95565092989985689</v>
+        <v>0.95677498467198041</v>
       </c>
       <c r="M23" s="5">
         <v>12056</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8619</v>
+        <v>8634</v>
       </c>
       <c r="P23" s="5">
-        <v>11904</v>
+        <v>11919</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.98739216987392164</v>
+        <v>0.98863636363636365</v>
       </c>
       <c r="R23" s="5">
         <v>9480</v>
@@ -4064,14 +4064,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6642</v>
+        <v>6657</v>
       </c>
       <c r="U23" s="5">
-        <v>9416</v>
+        <v>9431</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.99324894514767936</v>
+        <v>0.99483122362869203</v>
       </c>
       <c r="W23" s="5">
         <v>9764</v>
@@ -4081,14 +4081,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6664</v>
+        <v>6679</v>
       </c>
       <c r="Z23" s="5">
-        <v>9492</v>
+        <v>9507</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.97214256452273662</v>
+        <v>0.97367882015567386</v>
       </c>
       <c r="AB23" s="5">
         <v>12327</v>
@@ -4098,14 +4098,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8914</v>
+        <v>8936</v>
       </c>
       <c r="AE23" s="5">
-        <v>12132</v>
+        <v>12154</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.98418106595278654</v>
+        <v>0.98596576620426701</v>
       </c>
       <c r="AG23" s="5">
         <v>9618</v>
@@ -4115,14 +4115,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6690</v>
+        <v>6713</v>
       </c>
       <c r="AJ23" s="5">
-        <v>9419</v>
+        <v>9442</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.97930962778124353</v>
+        <v>0.98170097733416506</v>
       </c>
       <c r="AL23" s="5">
         <v>9741</v>
@@ -4132,14 +4132,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6920</v>
+        <v>6956</v>
       </c>
       <c r="AO23" s="5">
-        <v>9562</v>
+        <v>9598</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.98162406323786056</v>
+        <v>0.98531978236320705</v>
       </c>
       <c r="AQ23" s="5">
         <v>12556</v>
@@ -4149,14 +4149,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8992</v>
+        <v>9053</v>
       </c>
       <c r="AT23" s="5">
-        <v>12319</v>
+        <v>12380</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.98112456196240838</v>
+        <v>0.98598279706913028</v>
       </c>
       <c r="AV23" s="5">
         <v>9718</v>
@@ -4166,14 +4166,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>2687</v>
+        <v>2765</v>
       </c>
       <c r="AY23" s="5">
-        <v>9551</v>
+        <v>9629</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.9828153941140152</v>
+        <v>0.99084173698291833</v>
       </c>
       <c r="BA23" s="5">
         <v>10107</v>
@@ -4183,14 +4183,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6788</v>
+        <v>6891</v>
       </c>
       <c r="BD23" s="5">
-        <v>9720</v>
+        <v>9823</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.96170970614425644</v>
+        <v>0.97190066290689625</v>
       </c>
       <c r="BF23" s="5">
         <v>13018</v>
@@ -4200,14 +4200,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>8978</v>
+        <v>9184</v>
       </c>
       <c r="BI23" s="5">
-        <v>12298</v>
+        <v>12504</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.94469196497157781</v>
+        <v>0.96051620832693196</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>5542</v>
+        <v>5545</v>
       </c>
       <c r="F24" s="5">
-        <v>6895</v>
+        <v>6898</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.99322961682512245</v>
+        <v>0.99366176894266778</v>
       </c>
       <c r="H24" s="5">
         <v>7059</v>
@@ -4242,14 +4242,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>5547</v>
+        <v>5553</v>
       </c>
       <c r="K24" s="5">
-        <v>6957</v>
+        <v>6963</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.98555036124096895</v>
+        <v>0.98640033999150023</v>
       </c>
       <c r="M24" s="5">
         <v>8056</v>
@@ -4259,14 +4259,14 @@
       </c>
       <c r="O24" s="3">
         <f t="shared" si="4"/>
-        <v>5538</v>
+        <v>5547</v>
       </c>
       <c r="P24" s="5">
-        <v>7953</v>
+        <v>7962</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="5"/>
-        <v>0.98721449851042697</v>
+        <v>0.98833167825223434</v>
       </c>
       <c r="R24" s="5">
         <v>7134</v>
@@ -4276,14 +4276,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>4976</v>
+        <v>4983</v>
       </c>
       <c r="U24" s="5">
-        <v>7032</v>
+        <v>7039</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.98570227081581163</v>
+        <v>0.98668348752453039</v>
       </c>
       <c r="W24" s="5">
         <v>7208</v>
@@ -4293,14 +4293,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>4870</v>
+        <v>4878</v>
       </c>
       <c r="Z24" s="5">
-        <v>7072</v>
+        <v>7080</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.98113207547169812</v>
+        <v>0.98224195338512765</v>
       </c>
       <c r="AB24" s="5">
         <v>8228</v>
@@ -4310,14 +4310,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5788</v>
+        <v>5803</v>
       </c>
       <c r="AE24" s="5">
-        <v>8095</v>
+        <v>8110</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.98383568303354396</v>
+        <v>0.98565872630043749</v>
       </c>
       <c r="AG24" s="5">
         <v>7344</v>
@@ -4327,14 +4327,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4981</v>
+        <v>4998</v>
       </c>
       <c r="AJ24" s="5">
-        <v>7186</v>
+        <v>7203</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.97848583877995643</v>
+        <v>0.9808006535947712</v>
       </c>
       <c r="AL24" s="5">
         <v>7506</v>
@@ -4344,14 +4344,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4934</v>
+        <v>4954</v>
       </c>
       <c r="AO24" s="5">
-        <v>7290</v>
+        <v>7310</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.97122302158273377</v>
+        <v>0.97388755662136961</v>
       </c>
       <c r="AQ24" s="5">
         <v>8509</v>
@@ -4361,14 +4361,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5965</v>
+        <v>5995</v>
       </c>
       <c r="AT24" s="5">
-        <v>8291</v>
+        <v>8321</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.97438006816312139</v>
+        <v>0.97790574685626985</v>
       </c>
       <c r="AV24" s="5">
         <v>7570</v>
@@ -4378,14 +4378,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>1287</v>
+        <v>1316</v>
       </c>
       <c r="AY24" s="5">
-        <v>7330</v>
+        <v>7359</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.96829590488771466</v>
+        <v>0.97212681638044918</v>
       </c>
       <c r="BA24" s="5">
         <v>7648</v>
@@ -4395,14 +4395,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>5044</v>
+        <v>5081</v>
       </c>
       <c r="BD24" s="5">
-        <v>7467</v>
+        <v>7504</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.97633368200836823</v>
+        <v>0.98117154811715479</v>
       </c>
       <c r="BF24" s="5">
         <v>8767</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>6034</v>
+        <v>6104</v>
       </c>
       <c r="BI24" s="5">
-        <v>8488</v>
+        <v>8558</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.96817611497661682</v>
+        <v>0.97616060225846923</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>12834</v>
+        <v>12842</v>
       </c>
       <c r="F25" s="5">
-        <v>21352</v>
+        <v>21360</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.99436501653238951</v>
+        <v>0.99473757742280999</v>
       </c>
       <c r="H25" s="5">
         <v>21813</v>
@@ -4454,14 +4454,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>12800</v>
+        <v>12810</v>
       </c>
       <c r="K25" s="5">
-        <v>21544</v>
+        <v>21554</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.98766790446064279</v>
+        <v>0.98812634667400179</v>
       </c>
       <c r="M25" s="5">
         <v>29215</v>
@@ -4471,14 +4471,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>17622</v>
+        <v>17642</v>
       </c>
       <c r="P25" s="5">
-        <v>29070</v>
+        <v>29090</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>0.99503679616635288</v>
+        <v>0.99572137600547661</v>
       </c>
       <c r="R25" s="5">
         <v>21767</v>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>12416</v>
+        <v>12428</v>
       </c>
       <c r="U25" s="5">
-        <v>21630</v>
+        <v>21642</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>0.99370606881977308</v>
+        <v>0.99425736206183668</v>
       </c>
       <c r="W25" s="5">
         <v>22114</v>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>12231</v>
+        <v>12248</v>
       </c>
       <c r="Z25" s="5">
-        <v>21775</v>
+        <v>21792</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.98467034457809532</v>
+        <v>0.98543908836031469</v>
       </c>
       <c r="AB25" s="5">
         <v>29630</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>18448</v>
+        <v>18476</v>
       </c>
       <c r="AE25" s="5">
-        <v>29431</v>
+        <v>29459</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>0.99328383395207565</v>
+        <v>0.9942288221397233</v>
       </c>
       <c r="AG25" s="5">
         <v>22174</v>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>12800</v>
+        <v>12823</v>
       </c>
       <c r="AJ25" s="5">
-        <v>21912</v>
+        <v>21935</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.98818436006133314</v>
+        <v>0.98922161089564353</v>
       </c>
       <c r="AL25" s="5">
         <v>22503</v>
@@ -4556,14 +4556,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>12824</v>
+        <v>12854</v>
       </c>
       <c r="AO25" s="5">
-        <v>22292</v>
+        <v>22322</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99062347242589877</v>
+        <v>0.99195662800515483</v>
       </c>
       <c r="AQ25" s="5">
         <v>30294</v>
@@ -4573,14 +4573,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>18412</v>
+        <v>18466</v>
       </c>
       <c r="AT25" s="5">
-        <v>30078</v>
+        <v>30132</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>0.99286987522281644</v>
+        <v>0.99465240641711228</v>
       </c>
       <c r="AV25" s="5">
         <v>22740</v>
@@ -4590,14 +4590,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>4356</v>
+        <v>4408</v>
       </c>
       <c r="AY25" s="5">
-        <v>22619</v>
+        <v>22671</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.99467897977132802</v>
+        <v>0.99696569920844325</v>
       </c>
       <c r="BA25" s="5">
         <v>23197</v>
@@ -4607,14 +4607,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>12953</v>
+        <v>13035</v>
       </c>
       <c r="BD25" s="5">
-        <v>22851</v>
+        <v>22933</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.98508427813941457</v>
+        <v>0.98861921800232788</v>
       </c>
       <c r="BF25" s="5">
         <v>31043</v>
@@ -4624,14 +4624,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>18251</v>
+        <v>18448</v>
       </c>
       <c r="BI25" s="5">
-        <v>30370</v>
+        <v>30567</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>0.97832039429178885</v>
+        <v>0.98466643043520274</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>10250</v>
+        <v>10265</v>
       </c>
       <c r="F26" s="5">
-        <v>14437</v>
+        <v>14452</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.99209730621220449</v>
+        <v>0.99312809235843869</v>
       </c>
       <c r="H26" s="5">
         <v>14990</v>
@@ -4666,14 +4666,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>10156</v>
+        <v>10177</v>
       </c>
       <c r="K26" s="5">
-        <v>14780</v>
+        <v>14801</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.98599066044029349</v>
+        <v>0.98739159439626423</v>
       </c>
       <c r="M26" s="5">
         <v>28508</v>
@@ -4683,14 +4683,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>20185</v>
+        <v>20218</v>
       </c>
       <c r="P26" s="5">
-        <v>28479</v>
+        <v>28512</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99898274168654411</v>
+        <v>1.0001403114915111</v>
       </c>
       <c r="R26" s="5">
         <v>14719</v>
@@ -4700,14 +4700,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9847</v>
+        <v>9871</v>
       </c>
       <c r="U26" s="5">
-        <v>14602</v>
+        <v>14626</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.99205109042733886</v>
+        <v>0.99368163598070525</v>
       </c>
       <c r="W26" s="5">
         <v>15123</v>
@@ -4717,14 +4717,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9857</v>
+        <v>9880</v>
       </c>
       <c r="Z26" s="5">
-        <v>14825</v>
+        <v>14848</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.98029491503008659</v>
+        <v>0.98181577729286518</v>
       </c>
       <c r="AB26" s="5">
         <v>29054</v>
@@ -4734,14 +4734,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20751</v>
+        <v>20798</v>
       </c>
       <c r="AE26" s="5">
-        <v>28794</v>
+        <v>28841</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.99105114614166723</v>
+        <v>0.99266882356990427</v>
       </c>
       <c r="AG26" s="5">
         <v>14835</v>
@@ -4751,14 +4751,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9683</v>
+        <v>9717</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14644</v>
+        <v>14678</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.98712504213009777</v>
+        <v>0.98941691944725307</v>
       </c>
       <c r="AL26" s="5">
         <v>15316</v>
@@ -4768,14 +4768,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>9446</v>
+        <v>9494</v>
       </c>
       <c r="AO26" s="5">
-        <v>14922</v>
+        <v>14970</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.97427526769391481</v>
+        <v>0.97740924523374251</v>
       </c>
       <c r="AQ26" s="5">
         <v>29312</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>21039</v>
+        <v>21130</v>
       </c>
       <c r="AT26" s="5">
-        <v>29095</v>
+        <v>29186</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99259688864628826</v>
+        <v>0.99570141921397382</v>
       </c>
       <c r="AV26" s="5">
         <v>15164</v>
@@ -4802,14 +4802,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>2829</v>
+        <v>2919</v>
       </c>
       <c r="AY26" s="5">
-        <v>14825</v>
+        <v>14915</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.97764442099709836</v>
+        <v>0.98357953046689528</v>
       </c>
       <c r="BA26" s="5">
         <v>15499</v>
@@ -4819,14 +4819,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="20"/>
-        <v>10163</v>
+        <v>10291</v>
       </c>
       <c r="BD26" s="5">
-        <v>15001</v>
+        <v>15129</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.96786889476740434</v>
+        <v>0.97612749209626426</v>
       </c>
       <c r="BF26" s="5">
         <v>29635</v>
@@ -4836,14 +4836,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="22"/>
-        <v>20687</v>
+        <v>20972</v>
       </c>
       <c r="BI26" s="5">
-        <v>28845</v>
+        <v>29130</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.97334233170237894</v>
+        <v>0.98295933861987517</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>80340</v>
+        <v>80403</v>
       </c>
       <c r="F27" s="5">
-        <v>129697</v>
+        <v>129760</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.98908699896284547</v>
+        <v>0.9895674455493868</v>
       </c>
       <c r="H27" s="5">
         <v>134384</v>
@@ -4878,14 +4878,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>79596</v>
+        <v>79670</v>
       </c>
       <c r="K27" s="5">
-        <v>130543</v>
+        <v>130617</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.97141772830098816</v>
+        <v>0.97196838909393979</v>
       </c>
       <c r="M27" s="5">
         <v>190911</v>
@@ -4895,14 +4895,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>121927</v>
+        <v>122094</v>
       </c>
       <c r="P27" s="5">
-        <v>191348</v>
+        <v>191515</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>1.0022890247288003</v>
+        <v>1.0031637778860307</v>
       </c>
       <c r="R27" s="5">
         <v>131264</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>76453</v>
+        <v>76564</v>
       </c>
       <c r="U27" s="5">
-        <v>130406</v>
+        <v>130517</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99346355436372502</v>
+        <v>0.99430917844953681</v>
       </c>
       <c r="W27" s="5">
         <v>134144</v>
@@ -4929,14 +4929,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>76354</v>
+        <v>76481</v>
       </c>
       <c r="Z27" s="5">
-        <v>131824</v>
+        <v>131951</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.98270515267175573</v>
+        <v>0.9836518964694656</v>
       </c>
       <c r="AB27" s="5">
         <v>194609</v>
@@ -4946,14 +4946,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>125607</v>
+        <v>125880</v>
       </c>
       <c r="AE27" s="5">
-        <v>193571</v>
+        <v>193844</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99466622818060835</v>
+        <v>0.99606904100015925</v>
       </c>
       <c r="AG27" s="5">
         <v>134089</v>
@@ -4963,14 +4963,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>79198</v>
+        <v>79384</v>
       </c>
       <c r="AJ27" s="5">
-        <v>132213</v>
+        <v>132399</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.98600929233568746</v>
+        <v>0.98739643072884431</v>
       </c>
       <c r="AL27" s="5">
         <v>137688</v>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>80109</v>
+        <v>80358</v>
       </c>
       <c r="AO27" s="5">
-        <v>136498</v>
+        <v>136747</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.99135727151240483</v>
+        <v>0.99316570797745629</v>
       </c>
       <c r="AQ27" s="5">
         <v>200322</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>127904</v>
+        <v>128513</v>
       </c>
       <c r="AT27" s="5">
-        <v>199817</v>
+        <v>200426</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.99747905871546805</v>
+        <v>1.0005191641457254</v>
       </c>
       <c r="AV27" s="5">
         <v>139481</v>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>30596</v>
+        <v>31157</v>
       </c>
       <c r="AY27" s="5">
-        <v>137838</v>
+        <v>138399</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.98822061786193105</v>
+        <v>0.99224267104480179</v>
       </c>
       <c r="BA27" s="5">
         <v>143305</v>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="20"/>
-        <v>80754</v>
+        <v>81632</v>
       </c>
       <c r="BD27" s="5">
-        <v>139735</v>
+        <v>140613</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="21"/>
-        <v>0.97508809881022995</v>
+        <v>0.98121489131572515</v>
       </c>
       <c r="BF27" s="5">
         <v>208143</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>128661</v>
+        <v>130982</v>
       </c>
       <c r="BI27" s="5">
-        <v>200685</v>
+        <v>203006</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="23"/>
-        <v>0.96416886467476681</v>
+        <v>0.97531985221698547</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>189412</v>
+        <v>189490</v>
       </c>
       <c r="F28" s="5">
-        <v>434777</v>
+        <v>434855</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99374647153341733</v>
+        <v>0.99392475195022778</v>
       </c>
       <c r="H28" s="5">
         <v>447363</v>
@@ -5090,14 +5090,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>191772</v>
+        <v>191865</v>
       </c>
       <c r="K28" s="5">
-        <v>442464</v>
+        <v>442557</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.98904916141925014</v>
+        <v>0.98925704629126687</v>
       </c>
       <c r="M28" s="5">
         <v>722935</v>
@@ -5107,14 +5107,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>334537</v>
+        <v>334746</v>
       </c>
       <c r="P28" s="5">
-        <v>718852</v>
+        <v>719061</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99435218933929048</v>
+        <v>0.99464128863590784</v>
       </c>
       <c r="R28" s="5">
         <v>448339</v>
@@ -5124,14 +5124,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>186036</v>
+        <v>186181</v>
       </c>
       <c r="U28" s="5">
-        <v>445554</v>
+        <v>445699</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99378818260289647</v>
+        <v>0.99411159858946019</v>
       </c>
       <c r="W28" s="5">
         <v>458076</v>
@@ -5141,14 +5141,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>187658</v>
+        <v>187831</v>
       </c>
       <c r="Z28" s="5">
-        <v>450887</v>
+        <v>451060</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.9843060976781145</v>
+        <v>0.98468376426619164</v>
       </c>
       <c r="AB28" s="5">
         <v>737235</v>
@@ -5158,14 +5158,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>354168</v>
+        <v>354575</v>
       </c>
       <c r="AE28" s="5">
-        <v>731080</v>
+        <v>731487</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99165123739377536</v>
+        <v>0.99220330016887426</v>
       </c>
       <c r="AG28" s="5">
         <v>456666</v>
@@ -5175,14 +5175,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>193288</v>
+        <v>193562</v>
       </c>
       <c r="AJ28" s="5">
-        <v>451669</v>
+        <v>451943</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.9890576482593405</v>
+        <v>0.98965764913525422</v>
       </c>
       <c r="AL28" s="5">
         <v>468801</v>
@@ -5192,14 +5192,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>194147</v>
+        <v>194572</v>
       </c>
       <c r="AO28" s="5">
-        <v>464890</v>
+        <v>465315</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.99165744100375208</v>
+        <v>0.99256400903581687</v>
       </c>
       <c r="AQ28" s="5">
         <v>756132</v>
@@ -5209,14 +5209,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>354111</v>
+        <v>355162</v>
       </c>
       <c r="AT28" s="5">
-        <v>753124</v>
+        <v>754175</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.99602185861727843</v>
+        <v>0.99741182756449931</v>
       </c>
       <c r="AV28" s="5">
         <v>474991</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>65999</v>
+        <v>67028</v>
       </c>
       <c r="AY28" s="5">
-        <v>471034</v>
+        <v>472063</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.99166931583966855</v>
+        <v>0.99383567267590334</v>
       </c>
       <c r="BA28" s="5">
         <v>487540</v>
@@ -5243,14 +5243,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="20"/>
-        <v>198092</v>
+        <v>199708</v>
       </c>
       <c r="BD28" s="5">
-        <v>478666</v>
+        <v>480282</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="21"/>
-        <v>0.9817984165401813</v>
+        <v>0.98511301636788773</v>
       </c>
       <c r="BF28" s="5">
         <v>779284</v>
@@ -5260,14 +5260,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>355338</v>
+        <v>359924</v>
       </c>
       <c r="BI28" s="5">
-        <v>762876</v>
+        <v>767462</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.97894477494725929</v>
+        <v>0.98482966415324835</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5285,14 +5285,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>78379</v>
+        <v>78409</v>
       </c>
       <c r="F29" s="5">
-        <v>142712</v>
+        <v>142742</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99276531804774892</v>
+        <v>0.99297401079637149</v>
       </c>
       <c r="H29" s="5">
         <v>146310</v>
@@ -5302,14 +5302,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>77843</v>
+        <v>77881</v>
       </c>
       <c r="K29" s="5">
-        <v>144216</v>
+        <v>144254</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98568792290342422</v>
+        <v>0.9859476454104299</v>
       </c>
       <c r="M29" s="5">
         <v>194093</v>
@@ -5319,14 +5319,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>106460</v>
+        <v>106527</v>
       </c>
       <c r="P29" s="5">
-        <v>191887</v>
+        <v>191954</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98863431447811101</v>
+        <v>0.98897950982261085</v>
       </c>
       <c r="R29" s="5">
         <v>146918</v>
@@ -5336,14 +5336,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>77458</v>
+        <v>77509</v>
       </c>
       <c r="U29" s="5">
-        <v>145202</v>
+        <v>145253</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98832001524660018</v>
+        <v>0.98866714766059982</v>
       </c>
       <c r="W29" s="5">
         <v>149105</v>
@@ -5353,14 +5353,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>75598</v>
+        <v>75659</v>
       </c>
       <c r="Z29" s="5">
-        <v>146572</v>
+        <v>146633</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98301197142952956</v>
+        <v>0.9834210791053285</v>
       </c>
       <c r="AB29" s="5">
         <v>197403</v>
@@ -5370,14 +5370,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>110014</v>
+        <v>110136</v>
       </c>
       <c r="AE29" s="5">
-        <v>194880</v>
+        <v>195002</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.98721903922432785</v>
+        <v>0.98783706427967155</v>
       </c>
       <c r="AG29" s="5">
         <v>149309</v>
@@ -5387,14 +5387,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>78581</v>
+        <v>78680</v>
       </c>
       <c r="AJ29" s="5">
-        <v>147365</v>
+        <v>147464</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.98698002129811335</v>
+        <v>0.98764307576904276</v>
       </c>
       <c r="AL29" s="5">
         <v>152026</v>
@@ -5404,14 +5404,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>79643</v>
+        <v>79769</v>
       </c>
       <c r="AO29" s="5">
-        <v>152122</v>
+        <v>152248</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>1.0006314709326036</v>
+        <v>1.0014602765316458</v>
       </c>
       <c r="AQ29" s="5">
         <v>203571</v>
@@ -5421,14 +5421,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>113504</v>
+        <v>113810</v>
       </c>
       <c r="AT29" s="5">
-        <v>203141</v>
+        <v>203447</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.99788771485132954</v>
+        <v>0.99939087591061593</v>
       </c>
       <c r="AV29" s="5">
         <v>155780</v>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>25898</v>
+        <v>26275</v>
       </c>
       <c r="AY29" s="5">
-        <v>155247</v>
+        <v>155624</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.9965785081525228</v>
+        <v>0.99899858775195793</v>
       </c>
       <c r="BA29" s="5">
         <v>159604</v>
@@ -5455,14 +5455,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="20"/>
-        <v>82166</v>
+        <v>82775</v>
       </c>
       <c r="BD29" s="5">
-        <v>157725</v>
+        <v>158334</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="21"/>
-        <v>0.98822711210245362</v>
+        <v>0.99204280594471317</v>
       </c>
       <c r="BF29" s="5">
         <v>211893</v>
@@ -5472,14 +5472,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>113280</v>
+        <v>114648</v>
       </c>
       <c r="BI29" s="5">
-        <v>207487</v>
+        <v>208855</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.97920648629260998</v>
+        <v>0.98566257497888088</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>109351</v>
+        <v>109378</v>
       </c>
       <c r="F30" s="5">
-        <v>185358</v>
+        <v>185385</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.99509319704518129</v>
+        <v>0.99523814636660368</v>
       </c>
       <c r="H30" s="5">
         <v>190966</v>
@@ -5514,14 +5514,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>109623</v>
+        <v>109666</v>
       </c>
       <c r="K30" s="5">
-        <v>188342</v>
+        <v>188385</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98625933412230449</v>
+        <v>0.98648450509514785</v>
       </c>
       <c r="M30" s="5">
         <v>320227</v>
@@ -5531,14 +5531,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>196732</v>
+        <v>196824</v>
       </c>
       <c r="P30" s="5">
-        <v>318466</v>
+        <v>318558</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.99450077601201647</v>
+        <v>0.99478807221127508</v>
       </c>
       <c r="R30" s="5">
         <v>189502</v>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>105945</v>
+        <v>105995</v>
       </c>
       <c r="U30" s="5">
-        <v>188152</v>
+        <v>188202</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99287606463256328</v>
+        <v>0.99313991409061642</v>
       </c>
       <c r="W30" s="5">
         <v>194334</v>
@@ -5565,14 +5565,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>104601</v>
+        <v>104664</v>
       </c>
       <c r="Z30" s="5">
-        <v>190557</v>
+        <v>190620</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.98056438914446264</v>
+        <v>0.98088857328105217</v>
       </c>
       <c r="AB30" s="5">
         <v>325942</v>
@@ -5582,14 +5582,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>203236</v>
+        <v>203401</v>
       </c>
       <c r="AE30" s="5">
-        <v>323215</v>
+        <v>323380</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.99163348080333313</v>
+        <v>0.99213970583723488</v>
       </c>
       <c r="AG30" s="5">
         <v>192789</v>
@@ -5599,14 +5599,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>109091</v>
+        <v>109202</v>
       </c>
       <c r="AJ30" s="5">
-        <v>191125</v>
+        <v>191236</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.99136880216194911</v>
+        <v>0.99194456115234786</v>
       </c>
       <c r="AL30" s="5">
         <v>197994</v>
@@ -5616,14 +5616,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>108739</v>
+        <v>108908</v>
       </c>
       <c r="AO30" s="5">
-        <v>196030</v>
+        <v>196199</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.99008050749012599</v>
+        <v>0.99093406870915279</v>
       </c>
       <c r="AQ30" s="5">
         <v>333633</v>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>205682</v>
+        <v>206141</v>
       </c>
       <c r="AT30" s="5">
-        <v>331973</v>
+        <v>332432</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.99502447299877406</v>
+        <v>0.99640023618766727</v>
       </c>
       <c r="AV30" s="5">
         <v>198460</v>
@@ -5650,14 +5650,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>36851</v>
+        <v>37308</v>
       </c>
       <c r="AY30" s="5">
-        <v>197146</v>
+        <v>197603</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.99337901844200338</v>
+        <v>0.99568174947092614</v>
       </c>
       <c r="BA30" s="5">
         <v>203942</v>
@@ -5667,14 +5667,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="20"/>
-        <v>109134</v>
+        <v>109878</v>
       </c>
       <c r="BD30" s="5">
-        <v>200143</v>
+        <v>200887</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="21"/>
-        <v>0.98137215482833351</v>
+        <v>0.98502025085563538</v>
       </c>
       <c r="BF30" s="5">
         <v>342999</v>
@@ -5684,14 +5684,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>203808</v>
+        <v>206326</v>
       </c>
       <c r="BI30" s="5">
-        <v>334614</v>
+        <v>337132</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.97555386458852644</v>
+        <v>0.98289499386295587</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>37031</v>
+        <v>37043</v>
       </c>
       <c r="F31" s="5">
-        <v>83260</v>
+        <v>83272</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0045485805291796</v>
+        <v>1.0046933629332915</v>
       </c>
       <c r="H31" s="5">
         <v>85478</v>
@@ -5726,14 +5726,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35501</v>
+        <v>35514</v>
       </c>
       <c r="K31" s="5">
-        <v>84767</v>
+        <v>84780</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.99168207024029575</v>
+        <v>0.99183415615713988</v>
       </c>
       <c r="M31" s="5">
         <v>149930</v>
@@ -5743,14 +5743,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>75443</v>
+        <v>75491</v>
       </c>
       <c r="P31" s="5">
-        <v>151054</v>
+        <v>151102</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0074968318548656</v>
+        <v>1.0078169812579203</v>
       </c>
       <c r="R31" s="5">
         <v>83981</v>
@@ -5760,14 +5760,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34281</v>
+        <v>34297</v>
       </c>
       <c r="U31" s="5">
-        <v>84088</v>
+        <v>84104</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>1.0012740977125778</v>
+        <v>1.0014646169967016</v>
       </c>
       <c r="W31" s="5">
         <v>85994</v>
@@ -5777,14 +5777,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>33887</v>
+        <v>33913</v>
       </c>
       <c r="Z31" s="5">
-        <v>85462</v>
+        <v>85488</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.99381352187361904</v>
+        <v>0.9941158685489685</v>
       </c>
       <c r="AB31" s="5">
         <v>153633</v>
@@ -5794,14 +5794,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>78006</v>
+        <v>78093</v>
       </c>
       <c r="AE31" s="5">
-        <v>153734</v>
+        <v>153821</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0006574108427226</v>
+        <v>1.0012236954300182</v>
       </c>
       <c r="AG31" s="5">
         <v>85109</v>
@@ -5811,14 +5811,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>35671</v>
+        <v>35708</v>
       </c>
       <c r="AJ31" s="5">
-        <v>85488</v>
+        <v>85525</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>1.0044531130667731</v>
+        <v>1.0048878496986218</v>
       </c>
       <c r="AL31" s="5">
         <v>88549</v>
@@ -5828,14 +5828,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>34734</v>
+        <v>34777</v>
       </c>
       <c r="AO31" s="5">
-        <v>88031</v>
+        <v>88074</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.99415013156557386</v>
+        <v>0.99463573840472508</v>
       </c>
       <c r="AQ31" s="5">
         <v>156407</v>
@@ -5845,14 +5845,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>78383</v>
+        <v>78559</v>
       </c>
       <c r="AT31" s="5">
-        <v>157592</v>
+        <v>157768</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>1.0075763872460952</v>
+        <v>1.0087016565754729</v>
       </c>
       <c r="AV31" s="5">
         <v>87916</v>
@@ -5862,14 +5862,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>16711</v>
+        <v>16822</v>
       </c>
       <c r="AY31" s="5">
-        <v>88137</v>
+        <v>88248</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>1.0025137631375405</v>
+        <v>1.003776331953228</v>
       </c>
       <c r="BA31" s="5">
         <v>90084</v>
@@ -5879,14 +5879,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="20"/>
-        <v>35343</v>
+        <v>35545</v>
       </c>
       <c r="BD31" s="5">
-        <v>89821</v>
+        <v>90023</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="21"/>
-        <v>0.99708050264197856</v>
+        <v>0.9993228542249456</v>
       </c>
       <c r="BF31" s="5">
         <v>159779</v>
@@ -5896,14 +5896,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>78766</v>
+        <v>79868</v>
       </c>
       <c r="BI31" s="5">
-        <v>158539</v>
+        <v>159641</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>0.99223928050619914</v>
+        <v>0.99913630702407696</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>107532</v>
+        <v>107551</v>
       </c>
       <c r="F32" s="5">
-        <v>230826</v>
+        <v>230845</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.99487961933331615</v>
+        <v>0.99496151094330509</v>
       </c>
       <c r="H32" s="5">
         <v>238678</v>
@@ -5938,14 +5938,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>107608</v>
+        <v>107632</v>
       </c>
       <c r="K32" s="5">
-        <v>235344</v>
+        <v>235368</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98603138957088632</v>
+        <v>0.98613194345519906</v>
       </c>
       <c r="M32" s="5">
         <v>498323</v>
@@ -5955,14 +5955,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>270422</v>
+        <v>270506</v>
       </c>
       <c r="P32" s="5">
-        <v>495787</v>
+        <v>495871</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99491093126345764</v>
+        <v>0.9950794966317027</v>
       </c>
       <c r="R32" s="5">
         <v>234167</v>
@@ -5972,14 +5972,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>102996</v>
+        <v>103031</v>
       </c>
       <c r="U32" s="5">
-        <v>232935</v>
+        <v>232970</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.9947387975248434</v>
+        <v>0.99488826350425119</v>
       </c>
       <c r="W32" s="5">
         <v>242821</v>
@@ -5989,14 +5989,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>103597</v>
+        <v>103643</v>
       </c>
       <c r="Z32" s="5">
-        <v>237340</v>
+        <v>237386</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97742781719867722</v>
+        <v>0.97761725715650627</v>
       </c>
       <c r="AB32" s="5">
         <v>507064</v>
@@ -6006,14 +6006,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>280636</v>
+        <v>280812</v>
       </c>
       <c r="AE32" s="5">
-        <v>504857</v>
+        <v>505033</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99564749222977766</v>
+        <v>0.99599458845431743</v>
       </c>
       <c r="AG32" s="5">
         <v>238186</v>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>105864</v>
+        <v>105956</v>
       </c>
       <c r="AJ32" s="5">
-        <v>236700</v>
+        <v>236792</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99376117823885535</v>
+        <v>0.99414743099930303</v>
       </c>
       <c r="AL32" s="5">
         <v>247675</v>
@@ -6040,14 +6040,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>106108</v>
+        <v>106240</v>
       </c>
       <c r="AO32" s="5">
-        <v>246223</v>
+        <v>246355</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.99413747855051982</v>
+        <v>0.99467043504592711</v>
       </c>
       <c r="AQ32" s="5">
         <v>518099</v>
@@ -6057,14 +6057,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>279289</v>
+        <v>279790</v>
       </c>
       <c r="AT32" s="5">
-        <v>518995</v>
+        <v>519496</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>1.0017293992074874</v>
+        <v>1.0026963958625668</v>
       </c>
       <c r="AV32" s="5">
         <v>246693</v>
@@ -6074,14 +6074,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>42299</v>
+        <v>42585</v>
       </c>
       <c r="AY32" s="5">
-        <v>247135</v>
+        <v>247421</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>1.0017917006157451</v>
+        <v>1.0029510363082861</v>
       </c>
       <c r="BA32" s="5">
         <v>255610</v>
@@ -6091,14 +6091,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="20"/>
-        <v>109338</v>
+        <v>109812</v>
       </c>
       <c r="BD32" s="5">
-        <v>254077</v>
+        <v>254551</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="21"/>
-        <v>0.99400258205860492</v>
+        <v>0.99585696960212822</v>
       </c>
       <c r="BF32" s="5">
         <v>535637</v>
@@ -6108,14 +6108,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>274679</v>
+        <v>277363</v>
       </c>
       <c r="BI32" s="5">
-        <v>528532</v>
+        <v>531216</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.98673541969654821</v>
+        <v>0.99174627592940745</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6133,14 +6133,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112688</v>
+        <v>112703</v>
       </c>
       <c r="F33" s="5">
-        <v>717056</v>
+        <v>717071</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>1.0017644766014755</v>
+        <v>1.0017854323805904</v>
       </c>
       <c r="H33" s="5">
         <v>726544</v>
@@ -6150,14 +6150,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>106306</v>
+        <v>106328</v>
       </c>
       <c r="K33" s="5">
-        <v>729425</v>
+        <v>729447</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>1.0039653482789754</v>
+        <v>1.003995628619877</v>
       </c>
       <c r="M33" s="5">
         <v>1152516</v>
@@ -6167,14 +6167,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>203658</v>
+        <v>203704</v>
       </c>
       <c r="P33" s="5">
-        <v>1155986</v>
+        <v>1156032</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0030108041884018</v>
+        <v>1.0030507168664036</v>
       </c>
       <c r="R33" s="5">
         <v>733468</v>
@@ -6184,14 +6184,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>105055</v>
+        <v>105090</v>
       </c>
       <c r="U33" s="5">
-        <v>736342</v>
+        <v>736377</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0039183713536242</v>
+        <v>1.0039660898634979</v>
       </c>
       <c r="W33" s="5">
         <v>745690</v>
@@ -6201,14 +6201,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>105201</v>
+        <v>105249</v>
       </c>
       <c r="Z33" s="5">
-        <v>746158</v>
+        <v>746206</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>1.0006276066461934</v>
+        <v>1.0006919765586235</v>
       </c>
       <c r="AB33" s="5">
         <v>1180887</v>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>209436</v>
+        <v>209538</v>
       </c>
       <c r="AE33" s="5">
-        <v>1182508</v>
+        <v>1182610</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0013726969642311</v>
+        <v>1.0014590727139854</v>
       </c>
       <c r="AG33" s="5">
         <v>749948</v>
@@ -6235,14 +6235,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>110917</v>
+        <v>110999</v>
       </c>
       <c r="AJ33" s="5">
-        <v>750772</v>
+        <v>750854</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>1.0010987428461706</v>
+        <v>1.001208083760474</v>
       </c>
       <c r="AL33" s="5">
         <v>765123</v>
@@ -6252,14 +6252,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>110809</v>
+        <v>110929</v>
       </c>
       <c r="AO33" s="5">
-        <v>773672</v>
+        <v>773792</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>1.0111733668965643</v>
+        <v>1.0113302044246482</v>
       </c>
       <c r="AQ33" s="5">
         <v>1217820</v>
@@ -6269,14 +6269,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>216403</v>
+        <v>216740</v>
       </c>
       <c r="AT33" s="5">
-        <v>1225433</v>
+        <v>1225770</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>1.0062513343515462</v>
+        <v>1.0065280583337439</v>
       </c>
       <c r="AV33" s="5">
         <v>779865</v>
@@ -6286,14 +6286,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>72029</v>
+        <v>72401</v>
       </c>
       <c r="AY33" s="5">
-        <v>784558</v>
+        <v>784930</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>1.0060177081930848</v>
+        <v>1.0064947138286755</v>
       </c>
       <c r="BA33" s="5">
         <v>794982</v>
@@ -6303,14 +6303,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="20"/>
-        <v>107704</v>
+        <v>108345</v>
       </c>
       <c r="BD33" s="5">
-        <v>799540</v>
+        <v>800181</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="21"/>
-        <v>1.0057334631475934</v>
+        <v>1.0065397707117898</v>
       </c>
       <c r="BF33" s="5">
         <v>1258934</v>
@@ -6320,14 +6320,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>229367</v>
+        <v>231815</v>
       </c>
       <c r="BI33" s="5">
-        <v>1258893</v>
+        <v>1261341</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>0.99996743276454525</v>
+        <v>1.001911935018039</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6533,14 +6533,14 @@
       </c>
       <c r="E35" s="3">
         <f t="shared" ref="E35:E47" si="24">F35-D35</f>
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="F35" s="5">
-        <v>12239</v>
+        <v>12240</v>
       </c>
       <c r="G35" s="4">
         <f t="shared" ref="G35:G48" si="25">F35/C35</f>
-        <v>0.99844999184206229</v>
+        <v>0.99853157121879588</v>
       </c>
       <c r="H35" s="5">
         <v>12343</v>
@@ -6550,14 +6550,14 @@
       </c>
       <c r="J35" s="3">
         <f t="shared" ref="J35:J47" si="26">K35-I35</f>
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="K35" s="5">
-        <v>12327</v>
+        <v>12329</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.9987037187069594</v>
+        <v>0.99886575386858945</v>
       </c>
       <c r="M35" s="5">
         <v>15097</v>
@@ -6567,14 +6567,14 @@
       </c>
       <c r="O35" s="3">
         <f t="shared" ref="O35:O47" si="28">P35-N35</f>
-        <v>2841</v>
+        <v>2844</v>
       </c>
       <c r="P35" s="5">
-        <v>15082</v>
+        <v>15085</v>
       </c>
       <c r="Q35" s="4">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99900642511757298</v>
+        <v>0.99920514009405847</v>
       </c>
       <c r="R35" s="5">
         <v>12455</v>
@@ -6584,14 +6584,14 @@
       </c>
       <c r="T35" s="3">
         <f t="shared" ref="T35:T47" si="30">U35-S35</f>
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="U35" s="5">
-        <v>12412</v>
+        <v>12415</v>
       </c>
       <c r="V35" s="4">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99654757125652349</v>
+        <v>0.99678843837816133</v>
       </c>
       <c r="W35" s="5">
         <v>12547</v>
@@ -6601,14 +6601,14 @@
       </c>
       <c r="Y35" s="3">
         <f t="shared" ref="Y35:Y47" si="32">Z35-X35</f>
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="Z35" s="5">
-        <v>12442</v>
+        <v>12444</v>
       </c>
       <c r="AA35" s="4">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.99163146568900928</v>
+        <v>0.99179086634255198</v>
       </c>
       <c r="AB35" s="5">
         <v>15257</v>
@@ -6618,14 +6618,14 @@
       </c>
       <c r="AD35" s="3">
         <f t="shared" ref="AD35:AD47" si="34">AE35-AC35</f>
-        <v>2837</v>
+        <v>2839</v>
       </c>
       <c r="AE35" s="5">
-        <v>15204</v>
+        <v>15206</v>
       </c>
       <c r="AF35" s="4">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99652618470210397</v>
+        <v>0.99665727207183585</v>
       </c>
       <c r="AG35" s="5">
         <v>12574</v>
@@ -6635,14 +6635,14 @@
       </c>
       <c r="AI35" s="3">
         <f t="shared" ref="AI35:AI47" si="36">AJ35-AH35</f>
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="AJ35" s="5">
-        <v>12531</v>
+        <v>12534</v>
       </c>
       <c r="AK35" s="4">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99658024494989661</v>
+        <v>0.99681883251153169</v>
       </c>
       <c r="AL35" s="5">
         <v>12702</v>
@@ -6652,14 +6652,14 @@
       </c>
       <c r="AN35" s="3">
         <f t="shared" ref="AN35:AN47" si="38">AO35-AM35</f>
-        <v>2085</v>
+        <v>2092</v>
       </c>
       <c r="AO35" s="5">
-        <v>12625</v>
+        <v>12632</v>
       </c>
       <c r="AP35" s="4">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.99393796252558653</v>
+        <v>0.99448905684144229</v>
       </c>
       <c r="AQ35" s="5">
         <v>15458</v>
@@ -6669,14 +6669,14 @@
       </c>
       <c r="AS35" s="3">
         <f t="shared" ref="AS35:AS47" si="40">AT35-AR35</f>
-        <v>2848</v>
+        <v>2864</v>
       </c>
       <c r="AT35" s="5">
-        <v>15420</v>
+        <v>15436</v>
       </c>
       <c r="AU35" s="4">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>0.99754172596713675</v>
+        <v>0.99857678871781597</v>
       </c>
       <c r="AV35" s="5">
         <v>12806</v>
@@ -6686,14 +6686,14 @@
       </c>
       <c r="AX35" s="3">
         <f t="shared" ref="AX35:AX47" si="42">AY35-AW35</f>
-        <v>2018</v>
+        <v>2036</v>
       </c>
       <c r="AY35" s="5">
-        <v>12706</v>
+        <v>12724</v>
       </c>
       <c r="AZ35" s="4">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>0.99219116039356547</v>
+        <v>0.99359675152272375</v>
       </c>
       <c r="BA35" s="5">
         <v>12915</v>
@@ -6703,14 +6703,14 @@
       </c>
       <c r="BC35" s="3">
         <f t="shared" ref="BC35:BC47" si="44">BD35-BB35</f>
-        <v>1887</v>
+        <v>1916</v>
       </c>
       <c r="BD35" s="5">
-        <v>12752</v>
+        <v>12781</v>
       </c>
       <c r="BE35" s="4">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.98737901664730932</v>
+        <v>0.98962446767324819</v>
       </c>
       <c r="BF35" s="5">
         <v>15661</v>
@@ -6720,14 +6720,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
-        <v>2679</v>
+        <v>2729</v>
       </c>
       <c r="BI35" s="5">
-        <v>15483</v>
+        <v>15533</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.98863418683353554</v>
+        <v>0.99182683098141877</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="24"/>
-        <v>278663</v>
+        <v>278769</v>
       </c>
       <c r="F36" s="5">
-        <v>954646</v>
+        <v>954752</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="25"/>
-        <v>1.0019269319171713</v>
+        <v>1.0020381817990995</v>
       </c>
       <c r="H36" s="5">
         <v>975466</v>
@@ -6762,14 +6762,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="26"/>
-        <v>271667</v>
+        <v>271796</v>
       </c>
       <c r="K36" s="5">
-        <v>971045</v>
+        <v>971174</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="27"/>
-        <v>0.99546780718138816</v>
+        <v>0.99560005166761323</v>
       </c>
       <c r="M36" s="5">
         <v>1668278</v>
@@ -6779,14 +6779,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="28"/>
-        <v>535495</v>
+        <v>535753</v>
       </c>
       <c r="P36" s="5">
-        <v>1671408</v>
+        <v>1671666</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="29"/>
-        <v>1.0018761861032754</v>
+        <v>1.0020308365871875</v>
       </c>
       <c r="R36" s="5">
         <v>976879</v>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="30"/>
-        <v>261803</v>
+        <v>261978</v>
       </c>
       <c r="U36" s="5">
-        <v>976259</v>
+        <v>976434</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="31"/>
-        <v>0.99936532569540337</v>
+        <v>0.99954446763621696</v>
       </c>
       <c r="W36" s="5">
         <v>1000117</v>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="32"/>
-        <v>264402</v>
+        <v>264600</v>
       </c>
       <c r="Z36" s="5">
-        <v>988795</v>
+        <v>988993</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98867932451903129</v>
+        <v>0.98887730135574137</v>
       </c>
       <c r="AB36" s="5">
         <v>1701420</v>
@@ -6830,14 +6830,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="34"/>
-        <v>554494</v>
+        <v>554944</v>
       </c>
       <c r="AE36" s="5">
-        <v>1700478</v>
+        <v>1700928</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99944634481785799</v>
+        <v>0.99971082977747994</v>
       </c>
       <c r="AG36" s="5">
         <v>996655</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
-        <v>273757</v>
+        <v>274088</v>
       </c>
       <c r="AJ36" s="5">
-        <v>995994</v>
+        <v>996325</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="37"/>
-        <v>0.999336781534232</v>
+        <v>0.99966889244522927</v>
       </c>
       <c r="AL36" s="5">
         <v>1027093</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="38"/>
-        <v>273743</v>
+        <v>274199</v>
       </c>
       <c r="AO36" s="5">
-        <v>1032229</v>
+        <v>1032685</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="39"/>
-        <v>1.0050005208875925</v>
+        <v>1.0054444923682666</v>
       </c>
       <c r="AQ36" s="5">
         <v>1750886</v>
@@ -6881,14 +6881,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="40"/>
-        <v>560444</v>
+        <v>561697</v>
       </c>
       <c r="AT36" s="5">
-        <v>1765915</v>
+        <v>1767168</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="41"/>
-        <v>1.0085836542184927</v>
+        <v>1.0092992919013575</v>
       </c>
       <c r="AV36" s="5">
         <v>1041088</v>
@@ -6898,14 +6898,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="42"/>
-        <v>166276</v>
+        <v>167539</v>
       </c>
       <c r="AY36" s="5">
-        <v>1048276</v>
+        <v>1049539</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="43"/>
-        <v>1.0069043154853383</v>
+        <v>1.0081174694166104</v>
       </c>
       <c r="BA36" s="5">
         <v>1070068</v>
@@ -6915,14 +6915,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="44"/>
-        <v>269228</v>
+        <v>271278</v>
       </c>
       <c r="BD36" s="5">
-        <v>1069198</v>
+        <v>1071248</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="45"/>
-        <v>0.99918696755720193</v>
+        <v>1.0011027336580478</v>
       </c>
       <c r="BF36" s="5">
         <v>1814069</v>
@@ -6932,14 +6932,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="46"/>
-        <v>547882</v>
+        <v>557196</v>
       </c>
       <c r="BI36" s="5">
-        <v>1799244</v>
+        <v>1808558</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="47"/>
-        <v>0.99182776399354156</v>
+        <v>0.9969620780686953</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6957,14 +6957,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="24"/>
-        <v>309205</v>
+        <v>309305</v>
       </c>
       <c r="F37" s="5">
-        <v>734685</v>
+        <v>734785</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="25"/>
-        <v>0.99085193157358109</v>
+        <v>0.99098679916058419</v>
       </c>
       <c r="H37" s="5">
         <v>747767</v>
@@ -6974,14 +6974,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="26"/>
-        <v>304825</v>
+        <v>304958</v>
       </c>
       <c r="K37" s="5">
-        <v>739820</v>
+        <v>739953</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="27"/>
-        <v>0.98937235796712075</v>
+        <v>0.98955022085756661</v>
       </c>
       <c r="M37" s="5">
         <v>922163</v>
@@ -6991,14 +6991,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="28"/>
-        <v>374867</v>
+        <v>375072</v>
       </c>
       <c r="P37" s="5">
-        <v>915827</v>
+        <v>916032</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="29"/>
-        <v>0.99312919733279259</v>
+        <v>0.99335150076504908</v>
       </c>
       <c r="R37" s="5">
         <v>751356</v>
@@ -7008,14 +7008,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="30"/>
-        <v>292773</v>
+        <v>293001</v>
       </c>
       <c r="U37" s="5">
-        <v>744793</v>
+        <v>745021</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="31"/>
-        <v>0.9912651259855515</v>
+        <v>0.99156857734549264</v>
       </c>
       <c r="W37" s="5">
         <v>760191</v>
@@ -7025,14 +7025,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="32"/>
-        <v>284996</v>
+        <v>285275</v>
       </c>
       <c r="Z37" s="5">
-        <v>750680</v>
+        <v>750959</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98748867061041234</v>
+        <v>0.98785568363740162</v>
       </c>
       <c r="AB37" s="5">
         <v>938023</v>
@@ -7042,14 +7042,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="34"/>
-        <v>392727</v>
+        <v>393174</v>
       </c>
       <c r="AE37" s="5">
-        <v>930226</v>
+        <v>930673</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="35"/>
-        <v>0.99168783707862174</v>
+        <v>0.9921643712360998</v>
       </c>
       <c r="AG37" s="5">
         <v>763648</v>
@@ -7059,14 +7059,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
-        <v>299915</v>
+        <v>300379</v>
       </c>
       <c r="AJ37" s="5">
-        <v>756339</v>
+        <v>756803</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="37"/>
-        <v>0.99042883632249412</v>
+        <v>0.99103644611129738</v>
       </c>
       <c r="AL37" s="5">
         <v>773685</v>
@@ -7076,14 +7076,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="38"/>
-        <v>290160</v>
+        <v>290841</v>
       </c>
       <c r="AO37" s="5">
-        <v>769620</v>
+        <v>770301</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="39"/>
-        <v>0.99474592372864923</v>
+        <v>0.99562612691211538</v>
       </c>
       <c r="AQ37" s="5">
         <v>957323</v>
@@ -7093,14 +7093,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="40"/>
-        <v>390468</v>
+        <v>391794</v>
       </c>
       <c r="AT37" s="5">
-        <v>952731</v>
+        <v>954057</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99520329084332038</v>
+        <v>0.99658840328708287</v>
       </c>
       <c r="AV37" s="5">
         <v>783693</v>
@@ -7110,14 +7110,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="42"/>
-        <v>126962</v>
+        <v>128653</v>
       </c>
       <c r="AY37" s="5">
-        <v>777754</v>
+        <v>779445</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="43"/>
-        <v>0.99242177740518289</v>
+        <v>0.99457951008877199</v>
       </c>
       <c r="BA37" s="5">
         <v>794943</v>
@@ -7127,14 +7127,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="44"/>
-        <v>281589</v>
+        <v>284292</v>
       </c>
       <c r="BD37" s="5">
-        <v>783418</v>
+        <v>786121</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98550210518238412</v>
+        <v>0.98890234897344842</v>
       </c>
       <c r="BF37" s="5">
         <v>980352</v>
@@ -7144,14 +7144,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="46"/>
-        <v>383925</v>
+        <v>389865</v>
       </c>
       <c r="BI37" s="5">
-        <v>959042</v>
+        <v>964982</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="47"/>
-        <v>0.97826290964877927</v>
+        <v>0.98432195782739262</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7169,14 +7169,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="24"/>
-        <v>10019</v>
+        <v>10029</v>
       </c>
       <c r="F38" s="5">
-        <v>26190</v>
+        <v>26200</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="25"/>
-        <v>1.0049113652060471</v>
+        <v>1.0052950656127695</v>
       </c>
       <c r="H38" s="5">
         <v>26657</v>
@@ -7186,14 +7186,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="26"/>
-        <v>9691</v>
+        <v>9703</v>
       </c>
       <c r="K38" s="5">
-        <v>26488</v>
+        <v>26500</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="27"/>
-        <v>0.99366020182316095</v>
+        <v>0.9941103650073152</v>
       </c>
       <c r="M38" s="5">
         <v>40003</v>
@@ -7203,14 +7203,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="28"/>
-        <v>14620</v>
+        <v>14639</v>
       </c>
       <c r="P38" s="5">
-        <v>40096</v>
+        <v>40115</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="29"/>
-        <v>1.0023248256380772</v>
+        <v>1.0027997900157488</v>
       </c>
       <c r="R38" s="5">
         <v>26603</v>
@@ -7220,14 +7220,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="30"/>
-        <v>9159</v>
+        <v>9173</v>
       </c>
       <c r="U38" s="5">
-        <v>26627</v>
+        <v>26641</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="31"/>
-        <v>1.0009021538924181</v>
+        <v>1.001428410329662</v>
       </c>
       <c r="W38" s="5">
         <v>27177</v>
@@ -7237,14 +7237,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="32"/>
-        <v>9070</v>
+        <v>9091</v>
       </c>
       <c r="Z38" s="5">
-        <v>26863</v>
+        <v>26884</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="33"/>
-        <v>0.98844611252161751</v>
+        <v>0.98921882474150935</v>
       </c>
       <c r="AB38" s="5">
         <v>40627</v>
@@ -7254,14 +7254,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="34"/>
-        <v>15179</v>
+        <v>15212</v>
       </c>
       <c r="AE38" s="5">
-        <v>40692</v>
+        <v>40725</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0015999212346469</v>
+        <v>1.0024121889383908</v>
       </c>
       <c r="AG38" s="5">
         <v>26952</v>
@@ -7271,14 +7271,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
-        <v>9469</v>
+        <v>9502</v>
       </c>
       <c r="AJ38" s="5">
-        <v>27015</v>
+        <v>27048</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="37"/>
-        <v>1.0023374888691006</v>
+        <v>1.0035618878005343</v>
       </c>
       <c r="AL38" s="5">
         <v>27600</v>
@@ -7288,14 +7288,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="38"/>
-        <v>9055</v>
+        <v>9105</v>
       </c>
       <c r="AO38" s="5">
-        <v>27543</v>
+        <v>27593</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="39"/>
-        <v>0.99793478260869561</v>
+        <v>0.99974637681159417</v>
       </c>
       <c r="AQ38" s="5">
         <v>41434</v>
@@ -7305,14 +7305,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="40"/>
-        <v>15244</v>
+        <v>15327</v>
       </c>
       <c r="AT38" s="5">
-        <v>41668</v>
+        <v>41751</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0056475358401313</v>
+        <v>1.0076507216295796</v>
       </c>
       <c r="AV38" s="5">
         <v>27593</v>
@@ -7322,14 +7322,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="42"/>
-        <v>5307</v>
+        <v>5411</v>
       </c>
       <c r="AY38" s="5">
-        <v>27663</v>
+        <v>27767</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0025368752944588</v>
+        <v>1.0063059471605118</v>
       </c>
       <c r="BA38" s="5">
         <v>28279</v>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="44"/>
-        <v>8557</v>
+        <v>8737</v>
       </c>
       <c r="BD38" s="5">
-        <v>27859</v>
+        <v>28039</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="45"/>
-        <v>0.9851479896743166</v>
+        <v>0.99151313695675236</v>
       </c>
       <c r="BF38" s="5">
         <v>42642</v>
@@ -7356,14 +7356,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="46"/>
-        <v>14569</v>
+        <v>14986</v>
       </c>
       <c r="BI38" s="5">
-        <v>41568</v>
+        <v>41985</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="47"/>
-        <v>0.97481356409174058</v>
+        <v>0.98459265512874627</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7381,14 +7381,14 @@
       </c>
       <c r="E39" s="3">
         <f t="shared" si="24"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F39" s="5">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G39" s="4">
         <f t="shared" si="25"/>
-        <v>1.00390625</v>
+        <v>1.0078125</v>
       </c>
       <c r="H39" s="5">
         <v>262</v>
@@ -7432,14 +7432,14 @@
       </c>
       <c r="T39" s="3">
         <f t="shared" si="30"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U39" s="5">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" si="31"/>
-        <v>0.96212121212121215</v>
+        <v>0.96590909090909094</v>
       </c>
       <c r="W39" s="5">
         <v>265</v>
@@ -7449,14 +7449,14 @@
       </c>
       <c r="Y39" s="3">
         <f t="shared" si="32"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Z39" s="5">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA39" s="4">
         <f t="shared" si="33"/>
-        <v>0.96226415094339623</v>
+        <v>0.96603773584905661</v>
       </c>
       <c r="AB39" s="5">
         <v>322</v>
@@ -7466,14 +7466,14 @@
       </c>
       <c r="AD39" s="3">
         <f t="shared" si="34"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AE39" s="5">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AF39" s="4">
         <f t="shared" si="35"/>
-        <v>0.97204968944099379</v>
+        <v>0.97515527950310554</v>
       </c>
       <c r="AG39" s="5">
         <v>267</v>
@@ -7483,14 +7483,14 @@
       </c>
       <c r="AI39" s="3">
         <f t="shared" si="36"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AJ39" s="5">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AK39" s="4">
         <f t="shared" si="37"/>
-        <v>0.95131086142322097</v>
+        <v>0.9550561797752809</v>
       </c>
       <c r="AL39" s="5">
         <v>276</v>
@@ -7500,14 +7500,14 @@
       </c>
       <c r="AN39" s="3">
         <f t="shared" si="38"/>
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AO39" s="5">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AP39" s="4">
         <f t="shared" si="39"/>
-        <v>0.94927536231884058</v>
+        <v>0.95652173913043481</v>
       </c>
       <c r="AQ39" s="5">
         <v>338</v>
@@ -7517,14 +7517,14 @@
       </c>
       <c r="AS39" s="3">
         <f t="shared" si="40"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AT39" s="5">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AU39" s="4">
         <f t="shared" si="41"/>
-        <v>0.95562130177514792</v>
+        <v>0.95857988165680474</v>
       </c>
       <c r="AV39" s="5">
         <v>279</v>
@@ -7534,14 +7534,14 @@
       </c>
       <c r="AX39" s="3">
         <f t="shared" si="42"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AY39" s="5">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AZ39" s="4">
         <f t="shared" si="43"/>
-        <v>0.96057347670250892</v>
+        <v>0.97132616487455192</v>
       </c>
       <c r="BA39" s="5">
         <v>291</v>
@@ -7551,14 +7551,14 @@
       </c>
       <c r="BC39" s="3">
         <f t="shared" si="44"/>
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BD39" s="5">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="BE39" s="4">
         <f t="shared" si="45"/>
-        <v>0.92783505154639179</v>
+        <v>0.94158075601374569</v>
       </c>
       <c r="BF39" s="5">
         <v>344</v>
@@ -7568,14 +7568,14 @@
       </c>
       <c r="BH39" s="3">
         <f t="shared" si="46"/>
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="BI39" s="5">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="BJ39" s="4">
         <f t="shared" si="47"/>
-        <v>0.97093023255813948</v>
+        <v>0.98546511627906974</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="24"/>
-        <v>124961</v>
+        <v>125000</v>
       </c>
       <c r="F40" s="5">
-        <v>301621</v>
+        <v>301660</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="25"/>
-        <v>0.9925204183037506</v>
+        <v>0.99264875252555163</v>
       </c>
       <c r="H40" s="5">
         <v>306465</v>
@@ -7610,14 +7610,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="26"/>
-        <v>127436</v>
+        <v>127492</v>
       </c>
       <c r="K40" s="5">
-        <v>303009</v>
+        <v>303065</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="27"/>
-        <v>0.98872301894180414</v>
+        <v>0.98890574780154339</v>
       </c>
       <c r="M40" s="5">
         <v>361770</v>
@@ -7627,14 +7627,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="28"/>
-        <v>149793</v>
+        <v>149875</v>
       </c>
       <c r="P40" s="5">
-        <v>359306</v>
+        <v>359388</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="29"/>
-        <v>0.99318904276197584</v>
+        <v>0.99341570611161789</v>
       </c>
       <c r="R40" s="5">
         <v>306479</v>
@@ -7644,14 +7644,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="30"/>
-        <v>118060</v>
+        <v>118158</v>
       </c>
       <c r="U40" s="5">
-        <v>304773</v>
+        <v>304871</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="31"/>
-        <v>0.99443355009641765</v>
+        <v>0.99475331099357545</v>
       </c>
       <c r="W40" s="5">
         <v>309858</v>
@@ -7661,14 +7661,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="32"/>
-        <v>124370</v>
+        <v>124483</v>
       </c>
       <c r="Z40" s="5">
-        <v>306359</v>
+        <v>306472</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="33"/>
-        <v>0.98870773063790507</v>
+        <v>0.9890724138153606</v>
       </c>
       <c r="AB40" s="5">
         <v>365821</v>
@@ -7678,14 +7678,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="34"/>
-        <v>150652</v>
+        <v>150817</v>
       </c>
       <c r="AE40" s="5">
-        <v>363340</v>
+        <v>363505</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99321799459298399</v>
+        <v>0.99366903485584479</v>
       </c>
       <c r="AG40" s="5">
         <v>311342</v>
@@ -7695,14 +7695,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
-        <v>123670</v>
+        <v>123851</v>
       </c>
       <c r="AJ40" s="5">
-        <v>309028</v>
+        <v>309209</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="37"/>
-        <v>0.9925676587161385</v>
+        <v>0.99314901298250802</v>
       </c>
       <c r="AL40" s="5">
         <v>314792</v>
@@ -7712,14 +7712,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="38"/>
-        <v>124983</v>
+        <v>125254</v>
       </c>
       <c r="AO40" s="5">
-        <v>312861</v>
+        <v>313132</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99386579074436454</v>
+        <v>0.99472667666268522</v>
       </c>
       <c r="AQ40" s="5">
         <v>372144</v>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="40"/>
-        <v>157772</v>
+        <v>158315</v>
       </c>
       <c r="AT40" s="5">
-        <v>370473</v>
+        <v>371016</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99550980265703604</v>
+        <v>0.99696891525860953</v>
       </c>
       <c r="AV40" s="5">
         <v>317868</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="42"/>
-        <v>65545</v>
+        <v>66380</v>
       </c>
       <c r="AY40" s="5">
-        <v>315361</v>
+        <v>316196</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="43"/>
-        <v>0.99211307838473828</v>
+        <v>0.99473995494985334</v>
       </c>
       <c r="BA40" s="5">
         <v>321637</v>
@@ -7763,14 +7763,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="44"/>
-        <v>114051</v>
+        <v>115510</v>
       </c>
       <c r="BD40" s="5">
-        <v>316818</v>
+        <v>318277</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="45"/>
-        <v>0.98501727102292336</v>
+        <v>0.98955344068002127</v>
       </c>
       <c r="BF40" s="5">
         <v>380248</v>
@@ -7780,14 +7780,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="46"/>
-        <v>154732</v>
+        <v>157361</v>
       </c>
       <c r="BI40" s="5">
-        <v>371673</v>
+        <v>374302</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="47"/>
-        <v>0.97744892806799777</v>
+        <v>0.98436283688540116</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="24"/>
-        <v>370965</v>
+        <v>371057</v>
       </c>
       <c r="F41" s="5">
-        <v>976167</v>
+        <v>976259</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="25"/>
-        <v>0.99870477055716356</v>
+        <v>0.99879889465569505</v>
       </c>
       <c r="H41" s="5">
         <v>983280</v>
@@ -7822,14 +7822,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="26"/>
-        <v>379923</v>
+        <v>380032</v>
       </c>
       <c r="K41" s="5">
-        <v>980703</v>
+        <v>980812</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="27"/>
-        <v>0.99737917988772273</v>
+        <v>0.99749003335774145</v>
       </c>
       <c r="M41" s="5">
         <v>1084276</v>
@@ -7839,14 +7839,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="28"/>
-        <v>390598</v>
+        <v>390730</v>
       </c>
       <c r="P41" s="5">
-        <v>1083277</v>
+        <v>1083409</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="29"/>
-        <v>0.999078647871944</v>
+        <v>0.99920038809306855</v>
       </c>
       <c r="R41" s="5">
         <v>988018</v>
@@ -7856,14 +7856,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="30"/>
-        <v>349326</v>
+        <v>349465</v>
       </c>
       <c r="U41" s="5">
-        <v>988530</v>
+        <v>988669</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="31"/>
-        <v>1.0005182091824238</v>
+        <v>1.0006588948784334</v>
       </c>
       <c r="W41" s="5">
         <v>994033</v>
@@ -7873,14 +7873,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="32"/>
-        <v>343767</v>
+        <v>343948</v>
       </c>
       <c r="Z41" s="5">
-        <v>993699</v>
+        <v>993880</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="33"/>
-        <v>0.99966399505851411</v>
+        <v>0.99984608156872057</v>
       </c>
       <c r="AB41" s="5">
         <v>1097882</v>
@@ -7890,14 +7890,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="34"/>
-        <v>395059</v>
+        <v>395319</v>
       </c>
       <c r="AE41" s="5">
-        <v>1097856</v>
+        <v>1098116</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="35"/>
-        <v>0.99997631803782194</v>
+        <v>1.0002131376596028</v>
       </c>
       <c r="AG41" s="5">
         <v>1002140</v>
@@ -7907,14 +7907,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
-        <v>354708</v>
+        <v>354991</v>
       </c>
       <c r="AJ41" s="5">
-        <v>1002083</v>
+        <v>1002366</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99994312171952027</v>
+        <v>1.0002255173927794</v>
       </c>
       <c r="AL41" s="5">
         <v>1011306</v>
@@ -7924,14 +7924,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="38"/>
-        <v>343728</v>
+        <v>344110</v>
       </c>
       <c r="AO41" s="5">
-        <v>1015203</v>
+        <v>1015585</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="39"/>
-        <v>1.0038534330855349</v>
+        <v>1.0042311624770346</v>
       </c>
       <c r="AQ41" s="5">
         <v>1119532</v>
@@ -7941,14 +7941,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="40"/>
-        <v>397551</v>
+        <v>398231</v>
       </c>
       <c r="AT41" s="5">
-        <v>1124394</v>
+        <v>1125074</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="41"/>
-        <v>1.0043428861345634</v>
+        <v>1.00495028279674</v>
       </c>
       <c r="AV41" s="5">
         <v>1028062</v>
@@ -7958,14 +7958,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="42"/>
-        <v>150122</v>
+        <v>151073</v>
       </c>
       <c r="AY41" s="5">
-        <v>1029830</v>
+        <v>1030781</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="43"/>
-        <v>1.0017197406382106</v>
+        <v>1.0026447821240354</v>
       </c>
       <c r="BA41" s="5">
         <v>1037044</v>
@@ -7975,14 +7975,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="44"/>
-        <v>332260</v>
+        <v>333773</v>
       </c>
       <c r="BD41" s="5">
-        <v>1037077</v>
+        <v>1038590</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="45"/>
-        <v>1.0000318212149146</v>
+        <v>1.0014907757047917</v>
       </c>
       <c r="BF41" s="5">
         <v>1143357</v>
@@ -7992,14 +7992,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="46"/>
-        <v>396631</v>
+        <v>399850</v>
       </c>
       <c r="BI41" s="5">
-        <v>1140465</v>
+        <v>1143684</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99747060629357231</v>
+        <v>1.0002859999107889</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8017,14 +8017,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="24"/>
-        <v>9255</v>
+        <v>9258</v>
       </c>
       <c r="F42" s="5">
-        <v>19588</v>
+        <v>19591</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="25"/>
-        <v>0.99552754624923767</v>
+        <v>0.99568001626346814</v>
       </c>
       <c r="H42" s="5">
         <v>19882</v>
@@ -8034,14 +8034,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="26"/>
-        <v>9525</v>
+        <v>9528</v>
       </c>
       <c r="K42" s="5">
-        <v>19682</v>
+        <v>19685</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="27"/>
-        <v>0.98994064983402075</v>
+        <v>0.99009154008651046</v>
       </c>
       <c r="M42" s="5">
         <v>21930</v>
@@ -8051,14 +8051,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="28"/>
-        <v>9992</v>
+        <v>9997</v>
       </c>
       <c r="P42" s="5">
-        <v>21783</v>
+        <v>21788</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="29"/>
-        <v>0.99329685362517095</v>
+        <v>0.99352485180118555</v>
       </c>
       <c r="R42" s="5">
         <v>20021</v>
@@ -8068,14 +8068,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="30"/>
-        <v>8933</v>
+        <v>8938</v>
       </c>
       <c r="U42" s="5">
-        <v>19817</v>
+        <v>19822</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="31"/>
-        <v>0.98981069876629535</v>
+        <v>0.99006043654163134</v>
       </c>
       <c r="W42" s="5">
         <v>20153</v>
@@ -8085,14 +8085,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="32"/>
-        <v>8709</v>
+        <v>8713</v>
       </c>
       <c r="Z42" s="5">
-        <v>19916</v>
+        <v>19920</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="33"/>
-        <v>0.98823996427330918</v>
+        <v>0.98843844588894958</v>
       </c>
       <c r="AB42" s="5">
         <v>22238</v>
@@ -8102,14 +8102,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="34"/>
-        <v>10024</v>
+        <v>10032</v>
       </c>
       <c r="AE42" s="5">
-        <v>22079</v>
+        <v>22087</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="35"/>
-        <v>0.99285007644572354</v>
+        <v>0.99320982102707078</v>
       </c>
       <c r="AG42" s="5">
         <v>20276</v>
@@ -8119,14 +8119,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="36"/>
-        <v>9062</v>
+        <v>9068</v>
       </c>
       <c r="AJ42" s="5">
-        <v>20161</v>
+        <v>20167</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="37"/>
-        <v>0.9943282698757151</v>
+        <v>0.99462418623002569</v>
       </c>
       <c r="AL42" s="5">
         <v>20453</v>
@@ -8136,14 +8136,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="38"/>
-        <v>8762</v>
+        <v>8772</v>
       </c>
       <c r="AO42" s="5">
-        <v>20350</v>
+        <v>20360</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="39"/>
-        <v>0.99496406395149861</v>
+        <v>0.99545298978145014</v>
       </c>
       <c r="AQ42" s="5">
         <v>22621</v>
@@ -8153,14 +8153,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="40"/>
-        <v>10290</v>
+        <v>10308</v>
       </c>
       <c r="AT42" s="5">
-        <v>22591</v>
+        <v>22609</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="41"/>
-        <v>0.99867379868264006</v>
+        <v>0.99946951947305596</v>
       </c>
       <c r="AV42" s="5">
         <v>20714</v>
@@ -8170,14 +8170,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="42"/>
-        <v>3931</v>
+        <v>3957</v>
       </c>
       <c r="AY42" s="5">
-        <v>20627</v>
+        <v>20653</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="43"/>
-        <v>0.99579994206816647</v>
+        <v>0.99705513179492133</v>
       </c>
       <c r="BA42" s="5">
         <v>20927</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="44"/>
-        <v>8576</v>
+        <v>8636</v>
       </c>
       <c r="BD42" s="5">
-        <v>20738</v>
+        <v>20798</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="45"/>
-        <v>0.99096860515124008</v>
+        <v>0.99383571462703679</v>
       </c>
       <c r="BF42" s="5">
         <v>23165</v>
@@ -8204,14 +8204,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="46"/>
-        <v>10296</v>
+        <v>10425</v>
       </c>
       <c r="BI42" s="5">
-        <v>22813</v>
+        <v>22942</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="47"/>
-        <v>0.98480466220591412</v>
+        <v>0.99037340815886032</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="24"/>
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="F43" s="5">
-        <v>3887</v>
+        <v>3889</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="25"/>
-        <v>0.99310168625447115</v>
+        <v>0.99361267245784368</v>
       </c>
       <c r="H43" s="5">
         <v>3941</v>
@@ -8246,14 +8246,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="26"/>
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="K43" s="5">
-        <v>3927</v>
+        <v>3930</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="27"/>
-        <v>0.99644760213143868</v>
+        <v>0.99720883024613038</v>
       </c>
       <c r="M43" s="5">
         <v>4896</v>
@@ -8263,14 +8263,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="28"/>
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="P43" s="5">
-        <v>4863</v>
+        <v>4867</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="29"/>
-        <v>0.99325980392156865</v>
+        <v>0.99407679738562094</v>
       </c>
       <c r="R43" s="5">
         <v>3969</v>
@@ -8280,14 +8280,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="30"/>
-        <v>2157</v>
+        <v>2163</v>
       </c>
       <c r="U43" s="5">
-        <v>3930</v>
+        <v>3936</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="31"/>
-        <v>0.99017384731670444</v>
+        <v>0.99168556311413458</v>
       </c>
       <c r="W43" s="5">
         <v>4009</v>
@@ -8297,14 +8297,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="32"/>
-        <v>1961</v>
+        <v>1966</v>
       </c>
       <c r="Z43" s="5">
-        <v>3973</v>
+        <v>3978</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="33"/>
-        <v>0.99102020453978545</v>
+        <v>0.99226739835370414</v>
       </c>
       <c r="AB43" s="5">
         <v>4962</v>
@@ -8314,14 +8314,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="34"/>
-        <v>2688</v>
+        <v>2692</v>
       </c>
       <c r="AE43" s="5">
-        <v>4942</v>
+        <v>4946</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99596936719064888</v>
+        <v>0.99677549375251917</v>
       </c>
       <c r="AG43" s="5">
         <v>4018</v>
@@ -8331,14 +8331,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="36"/>
-        <v>2247</v>
+        <v>2253</v>
       </c>
       <c r="AJ43" s="5">
-        <v>4010</v>
+        <v>4016</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="37"/>
-        <v>0.99800895968143355</v>
+        <v>0.99950223992035836</v>
       </c>
       <c r="AL43" s="5">
         <v>4086</v>
@@ -8348,14 +8348,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="38"/>
-        <v>2152</v>
+        <v>2159</v>
       </c>
       <c r="AO43" s="5">
-        <v>4067</v>
+        <v>4074</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="39"/>
-        <v>0.99534997552618698</v>
+        <v>0.99706314243759175</v>
       </c>
       <c r="AQ43" s="5">
         <v>5072</v>
@@ -8365,14 +8365,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="40"/>
-        <v>2930</v>
+        <v>2943</v>
       </c>
       <c r="AT43" s="5">
-        <v>5068</v>
+        <v>5081</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="41"/>
-        <v>0.99921135646687698</v>
+        <v>1.0017744479495267</v>
       </c>
       <c r="AV43" s="5">
         <v>4151</v>
@@ -8382,14 +8382,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="42"/>
-        <v>1255</v>
+        <v>1278</v>
       </c>
       <c r="AY43" s="5">
-        <v>4096</v>
+        <v>4119</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="43"/>
-        <v>0.98675018067935438</v>
+        <v>0.99229101421344257</v>
       </c>
       <c r="BA43" s="5">
         <v>4249</v>
@@ -8399,14 +8399,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="44"/>
-        <v>2175</v>
+        <v>2204</v>
       </c>
       <c r="BD43" s="5">
-        <v>4143</v>
+        <v>4172</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="45"/>
-        <v>0.97505295363614963</v>
+        <v>0.98187808896210871</v>
       </c>
       <c r="BF43" s="5">
         <v>5295</v>
@@ -8416,14 +8416,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="46"/>
-        <v>2837</v>
+        <v>2921</v>
       </c>
       <c r="BI43" s="5">
-        <v>5050</v>
+        <v>5134</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="47"/>
-        <v>0.95372993389990557</v>
+        <v>0.96959395656279512</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="24"/>
-        <v>186022</v>
+        <v>186051</v>
       </c>
       <c r="F44" s="5">
-        <v>380039</v>
+        <v>380068</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="25"/>
-        <v>0.99087704477783167</v>
+        <v>0.99095265658161646</v>
       </c>
       <c r="H44" s="5">
         <v>388149</v>
@@ -8458,14 +8458,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="26"/>
-        <v>184516</v>
+        <v>184555</v>
       </c>
       <c r="K44" s="5">
-        <v>383320</v>
+        <v>383359</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="27"/>
-        <v>0.98755890134973945</v>
+        <v>0.98765937822846384</v>
       </c>
       <c r="M44" s="5">
         <v>456953</v>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="28"/>
-        <v>212126</v>
+        <v>212178</v>
       </c>
       <c r="P44" s="5">
-        <v>453932</v>
+        <v>453984</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="29"/>
-        <v>0.99338881679297431</v>
+        <v>0.99350261405439944</v>
       </c>
       <c r="R44" s="5">
         <v>388846</v>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="30"/>
-        <v>181409</v>
+        <v>181466</v>
       </c>
       <c r="U44" s="5">
-        <v>385503</v>
+        <v>385560</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="31"/>
-        <v>0.99140276613363643</v>
+        <v>0.99154935372872555</v>
       </c>
       <c r="W44" s="5">
         <v>393146</v>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="32"/>
-        <v>178550</v>
+        <v>178623</v>
       </c>
       <c r="Z44" s="5">
-        <v>388138</v>
+        <v>388211</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="33"/>
-        <v>0.98726172973907911</v>
+        <v>0.9874474113942403</v>
       </c>
       <c r="AB44" s="5">
         <v>465292</v>
@@ -8526,14 +8526,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="34"/>
-        <v>222915</v>
+        <v>223044</v>
       </c>
       <c r="AE44" s="5">
-        <v>460939</v>
+        <v>461068</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="35"/>
-        <v>0.99064458447598502</v>
+        <v>0.99092182973272702</v>
       </c>
       <c r="AG44" s="5">
         <v>393778</v>
@@ -8543,14 +8543,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
-        <v>181184</v>
+        <v>181326</v>
       </c>
       <c r="AJ44" s="5">
-        <v>391791</v>
+        <v>391933</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="37"/>
-        <v>0.99495400961963343</v>
+        <v>0.99531461889694195</v>
       </c>
       <c r="AL44" s="5">
         <v>398873</v>
@@ -8560,14 +8560,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="38"/>
-        <v>179888</v>
+        <v>180098</v>
       </c>
       <c r="AO44" s="5">
-        <v>401392</v>
+        <v>401602</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="39"/>
-        <v>1.0063152933389825</v>
+        <v>1.0068417767058688</v>
       </c>
       <c r="AQ44" s="5">
         <v>476819</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="40"/>
-        <v>223044</v>
+        <v>223449</v>
       </c>
       <c r="AT44" s="5">
-        <v>478683</v>
+        <v>479088</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="41"/>
-        <v>1.0039092401938681</v>
+        <v>1.0047586190986517</v>
       </c>
       <c r="AV44" s="5">
         <v>408878</v>
@@ -8594,14 +8594,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="42"/>
-        <v>74221</v>
+        <v>74799</v>
       </c>
       <c r="AY44" s="5">
-        <v>409599</v>
+        <v>410177</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="43"/>
-        <v>1.0017633621764928</v>
+        <v>1.0031769867784524</v>
       </c>
       <c r="BA44" s="5">
         <v>416024</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="44"/>
-        <v>179560</v>
+        <v>180567</v>
       </c>
       <c r="BD44" s="5">
-        <v>414626</v>
+        <v>415633</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="45"/>
-        <v>0.99663961694517622</v>
+        <v>0.99906015037593987</v>
       </c>
       <c r="BF44" s="5">
         <v>493955</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="46"/>
-        <v>228226</v>
+        <v>230745</v>
       </c>
       <c r="BI44" s="5">
-        <v>488191</v>
+        <v>490710</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="47"/>
-        <v>0.98833092083286944</v>
+        <v>0.99343057565972603</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8653,14 +8653,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="24"/>
-        <v>138448</v>
+        <v>138470</v>
       </c>
       <c r="F45" s="5">
-        <v>276942</v>
+        <v>276964</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="25"/>
-        <v>0.99800357482630375</v>
+        <v>0.99808285524836393</v>
       </c>
       <c r="H45" s="5">
         <v>280269</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="26"/>
-        <v>138768</v>
+        <v>138793</v>
       </c>
       <c r="K45" s="5">
-        <v>278895</v>
+        <v>278920</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="27"/>
-        <v>0.99509756698029395</v>
+        <v>0.99518676699884756</v>
       </c>
       <c r="M45" s="5">
         <v>334005</v>
@@ -8687,14 +8687,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="28"/>
-        <v>162491</v>
+        <v>162537</v>
       </c>
       <c r="P45" s="5">
-        <v>332227</v>
+        <v>332273</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="29"/>
-        <v>0.99467672639631144</v>
+        <v>0.99481444888549575</v>
       </c>
       <c r="R45" s="5">
         <v>281510</v>
@@ -8704,14 +8704,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="30"/>
-        <v>134330</v>
+        <v>134374</v>
       </c>
       <c r="U45" s="5">
-        <v>279911</v>
+        <v>279955</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="31"/>
-        <v>0.9943199175872971</v>
+        <v>0.99447621754111759</v>
       </c>
       <c r="W45" s="5">
         <v>284325</v>
@@ -8721,14 +8721,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="32"/>
-        <v>133155</v>
+        <v>133209</v>
       </c>
       <c r="Z45" s="5">
-        <v>281054</v>
+        <v>281108</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="33"/>
-        <v>0.98849555965884106</v>
+        <v>0.98868548316187466</v>
       </c>
       <c r="AB45" s="5">
         <v>338696</v>
@@ -8738,14 +8738,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="34"/>
-        <v>171892</v>
+        <v>172003</v>
       </c>
       <c r="AE45" s="5">
-        <v>335162</v>
+        <v>335273</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98956586437395189</v>
+        <v>0.98989359189361548</v>
       </c>
       <c r="AG45" s="5">
         <v>285325</v>
@@ -8755,14 +8755,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
-        <v>139592</v>
+        <v>139691</v>
       </c>
       <c r="AJ45" s="5">
-        <v>282791</v>
+        <v>282890</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="37"/>
-        <v>0.99111889950056953</v>
+        <v>0.99146587225094196</v>
       </c>
       <c r="AL45" s="5">
         <v>289428</v>
@@ -8772,14 +8772,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="38"/>
-        <v>135710</v>
+        <v>135885</v>
       </c>
       <c r="AO45" s="5">
-        <v>289544</v>
+        <v>289719</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="39"/>
-        <v>1.0004007905247592</v>
+        <v>1.0010054314026287</v>
       </c>
       <c r="AQ45" s="5">
         <v>348161</v>
@@ -8789,14 +8789,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="40"/>
-        <v>171505</v>
+        <v>171880</v>
       </c>
       <c r="AT45" s="5">
-        <v>347359</v>
+        <v>347734</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="41"/>
-        <v>0.99769646801336165</v>
+        <v>0.99877355591235084</v>
       </c>
       <c r="AV45" s="5">
         <v>296165</v>
@@ -8806,14 +8806,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="42"/>
-        <v>52732</v>
+        <v>53168</v>
       </c>
       <c r="AY45" s="5">
-        <v>294765</v>
+        <v>295201</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="43"/>
-        <v>0.99527290530616375</v>
+        <v>0.99674505765367283</v>
       </c>
       <c r="BA45" s="5">
         <v>300603</v>
@@ -8823,14 +8823,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="44"/>
-        <v>135352</v>
+        <v>136108</v>
       </c>
       <c r="BD45" s="5">
-        <v>298153</v>
+        <v>298909</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="45"/>
-        <v>0.99184971540536859</v>
+        <v>0.99436466036599769</v>
       </c>
       <c r="BF45" s="5">
         <v>359430</v>
@@ -8840,14 +8840,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="46"/>
-        <v>177671</v>
+        <v>179628</v>
       </c>
       <c r="BI45" s="5">
-        <v>353946</v>
+        <v>355903</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="47"/>
-        <v>0.9847425089725399</v>
+        <v>0.99018724090921739</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8865,14 +8865,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="24"/>
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="F46" s="5">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="25"/>
-        <v>1.0288065843621399</v>
+        <v>1.0292181069958848</v>
       </c>
       <c r="H46" s="5">
         <v>2594</v>
@@ -8882,14 +8882,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="26"/>
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="K46" s="5">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="27"/>
-        <v>1.0208172706245182</v>
+        <v>1.0212027756360833</v>
       </c>
       <c r="M46" s="5">
         <v>8454</v>
@@ -8899,14 +8899,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="28"/>
-        <v>5767</v>
+        <v>5769</v>
       </c>
       <c r="P46" s="5">
-        <v>8622</v>
+        <v>8624</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="29"/>
-        <v>1.0198722498225692</v>
+        <v>1.0201088242252188</v>
       </c>
       <c r="R46" s="5">
         <v>2484</v>
@@ -8916,14 +8916,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="30"/>
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="U46" s="5">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="31"/>
-        <v>1.0446859903381642</v>
+        <v>1.0462962962962963</v>
       </c>
       <c r="W46" s="5">
         <v>2748</v>
@@ -8933,14 +8933,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="32"/>
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="Z46" s="5">
-        <v>2703</v>
+        <v>2706</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="33"/>
-        <v>0.98362445414847166</v>
+        <v>0.98471615720524019</v>
       </c>
       <c r="AB46" s="5">
         <v>8770</v>
@@ -8950,14 +8950,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="34"/>
-        <v>5872</v>
+        <v>5878</v>
       </c>
       <c r="AE46" s="5">
-        <v>8858</v>
+        <v>8864</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0100342075256556</v>
+        <v>1.0107183580387686</v>
       </c>
       <c r="AG46" s="5">
         <v>2523</v>
@@ -8967,14 +8967,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2557</v>
+        <v>2562</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="37"/>
-        <v>1.0134760206103846</v>
+        <v>1.0154577883472058</v>
       </c>
       <c r="AL46" s="5">
         <v>2722</v>
@@ -8984,14 +8984,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="38"/>
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="AO46" s="5">
-        <v>2669</v>
+        <v>2679</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="39"/>
-        <v>0.98052902277736953</v>
+        <v>0.98420279206465833</v>
       </c>
       <c r="AQ46" s="5">
         <v>8967</v>
@@ -9001,14 +9001,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="40"/>
-        <v>5775</v>
+        <v>5796</v>
       </c>
       <c r="AT46" s="5">
-        <v>8995</v>
+        <v>9016</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="41"/>
-        <v>1.0031225604996097</v>
+        <v>1.0054644808743169</v>
       </c>
       <c r="AV46" s="5">
         <v>2626</v>
@@ -9018,14 +9018,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="42"/>
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="AY46" s="5">
-        <v>2629</v>
+        <v>2647</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="43"/>
-        <v>1.0011424219345011</v>
+        <v>1.0079969535415081</v>
       </c>
       <c r="BA46" s="5">
         <v>2791</v>
@@ -9035,14 +9035,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="44"/>
-        <v>1460</v>
+        <v>1482</v>
       </c>
       <c r="BD46" s="5">
-        <v>2679</v>
+        <v>2701</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="45"/>
-        <v>0.95987101397348618</v>
+        <v>0.96775349337155137</v>
       </c>
       <c r="BF46" s="5">
         <v>9093</v>
@@ -9052,14 +9052,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="46"/>
-        <v>5907</v>
+        <v>5978</v>
       </c>
       <c r="BI46" s="5">
-        <v>8977</v>
+        <v>9048</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="47"/>
-        <v>0.98724293412515118</v>
+        <v>0.99505113823820523</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9275,10 +9275,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="17"/>
+      <c r="B48" s="20"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>8623084</v>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3388733</v>
+        <v>3389913</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8583089</v>
+        <v>8584269</v>
       </c>
       <c r="G48" s="6">
         <f t="shared" si="25"/>
-        <v>0.99536186821327499</v>
+        <v>0.99549871020623248</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3395443</v>
+        <v>3396890</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8700216</v>
+        <v>8701663</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="27"/>
-        <v>0.99169018452844426</v>
+        <v>0.99185512016877919</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5480981</v>
+        <v>5483807</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>13322597</v>
+        <v>13325423</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" si="29"/>
-        <v>0.99753704300351065</v>
+        <v>0.99774864136406516</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3279680</v>
+        <v>3281777</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8730611</v>
+        <v>8732708</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" si="31"/>
-        <v>0.99543579592007059</v>
+        <v>0.99567488902180712</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9369,15 +9369,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3256575</v>
+        <v>3259113</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8828225</v>
+        <v>8830763</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" si="33"/>
-        <v>0.98831825947574115</v>
+        <v>0.98860238813609469</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9389,15 +9389,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5701313</v>
+        <v>5706714</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>13543086</v>
+        <v>13548487</v>
       </c>
       <c r="AF48" s="6">
         <f t="shared" si="35"/>
-        <v>0.99524361377767623</v>
+        <v>0.99564051820241461</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9409,15 +9409,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3373852</v>
+        <v>3378008</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8869339</v>
+        <v>8873495</v>
       </c>
       <c r="AK48" s="6">
         <f t="shared" si="37"/>
-        <v>0.99464344029182572</v>
+        <v>0.99510951089053123</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9429,15 +9429,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3368463</v>
+        <v>3374372</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>9133928</v>
+        <v>9139837</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" si="39"/>
-        <v>1.0007195947130385</v>
+        <v>1.0013669889212216</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9449,15 +9449,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>5759491</v>
+        <v>5773844</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>13998881</v>
+        <v>14013234</v>
       </c>
       <c r="AU48" s="6">
         <f t="shared" si="41"/>
-        <v>1.0015565432805387</v>
+        <v>1.0025834354346834</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9469,15 +9469,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>1446488</v>
+        <v>1461446</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>9245550</v>
+        <v>9260508</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" si="43"/>
-        <v>0.99945819508047185</v>
+        <v>1.00107517791892</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9489,15 +9489,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3367981</v>
+        <v>3391703</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>9397425</v>
+        <v>9421147</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" si="45"/>
-        <v>0.99226245564612137</v>
+        <v>0.99476723221766494</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9509,19 +9509,27 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5795272</v>
+        <v>5865929</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>14245034</v>
+        <v>14315691</v>
       </c>
       <c r="BJ48" s="6">
         <f t="shared" si="47"/>
-        <v>0.98714127686921804</v>
+        <v>0.99203761065120466</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="BF8:BJ8"/>
+    <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="AV8:AZ8"/>
+    <mergeCell ref="AQ8:AU8"/>
+    <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
@@ -9530,14 +9538,6 @@
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="BF8:BJ8"/>
-    <mergeCell ref="BA8:BE8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="AV8:AZ8"/>
-    <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="AG8:AK8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
